--- a/sitkana/Fixed Vessel Cases/Site 1 Optimal/results_df.xlsx
+++ b/sitkana/Fixed Vessel Cases/Site 1 Optimal/results_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T298"/>
+  <dimension ref="A1:T277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17642,1308 +17642,6 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B278" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C278" t="n">
-        <v>14</v>
-      </c>
-      <c r="D278" t="n">
-        <v>12.99559113215011</v>
-      </c>
-      <c r="E278" t="n">
-        <v>10.0402636072274</v>
-      </c>
-      <c r="F278" t="n">
-        <v>14</v>
-      </c>
-      <c r="G278" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H278" t="n">
-        <v>0.04355189505591559</v>
-      </c>
-      <c r="I278" t="n">
-        <v>14</v>
-      </c>
-      <c r="J278" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K278" t="n">
-        <v>6209.560000000001</v>
-      </c>
-      <c r="L278" t="n">
-        <v>19496.07069700147</v>
-      </c>
-      <c r="M278" t="n">
-        <v>7655.686525581573</v>
-      </c>
-      <c r="N278" t="n">
-        <v>1490.202744702</v>
-      </c>
-      <c r="O278" t="n">
-        <v>11182.8279696</v>
-      </c>
-      <c r="P278" t="n">
-        <v>48914.13986199999</v>
-      </c>
-      <c r="Q278" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R278" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S278" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T278" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B279" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C279" t="n">
-        <v>18</v>
-      </c>
-      <c r="D279" t="n">
-        <v>9.862366503899541</v>
-      </c>
-      <c r="E279" t="n">
-        <v>9.293565808940587</v>
-      </c>
-      <c r="F279" t="n">
-        <v>14</v>
-      </c>
-      <c r="G279" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H279" t="n">
-        <v>0.1742075802236624</v>
-      </c>
-      <c r="I279" t="n">
-        <v>14</v>
-      </c>
-      <c r="J279" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K279" t="n">
-        <v>2891.56</v>
-      </c>
-      <c r="L279" t="n">
-        <v>11761.96926324595</v>
-      </c>
-      <c r="M279" t="n">
-        <v>5319.413731221542</v>
-      </c>
-      <c r="N279" t="n">
-        <v>374.4457123995</v>
-      </c>
-      <c r="O279" t="n">
-        <v>4606.35457485</v>
-      </c>
-      <c r="P279" t="n">
-        <v>16031.772862</v>
-      </c>
-      <c r="Q279" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R279" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S279" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T279" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B280" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C280" t="n">
-        <v>10</v>
-      </c>
-      <c r="D280" t="n">
-        <v>9.282565094392938</v>
-      </c>
-      <c r="E280" t="n">
-        <v>10.0402636072274</v>
-      </c>
-      <c r="F280" t="n">
-        <v>14</v>
-      </c>
-      <c r="G280" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H280" t="n">
-        <v>0.04355189505591559</v>
-      </c>
-      <c r="I280" t="n">
-        <v>14</v>
-      </c>
-      <c r="J280" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K280" t="n">
-        <v>6209.560000000001</v>
-      </c>
-      <c r="L280" t="n">
-        <v>19496.07069700147</v>
-      </c>
-      <c r="M280" t="n">
-        <v>7655.686525581573</v>
-      </c>
-      <c r="N280" t="n">
-        <v>1490.202744702</v>
-      </c>
-      <c r="O280" t="n">
-        <v>11182.8279696</v>
-      </c>
-      <c r="P280" t="n">
-        <v>48914.13986199999</v>
-      </c>
-      <c r="Q280" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R280" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S280" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T280" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B281" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C281" t="n">
-        <v>18</v>
-      </c>
-      <c r="D281" t="n">
-        <v>2.914967211530838</v>
-      </c>
-      <c r="E281" t="n">
-        <v>9.856935437888509</v>
-      </c>
-      <c r="F281" t="n">
-        <v>14</v>
-      </c>
-      <c r="G281" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H281" t="n">
-        <v>0.8710379011183119</v>
-      </c>
-      <c r="I281" t="n">
-        <v>14</v>
-      </c>
-      <c r="J281" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K281" t="n">
-        <v>2006.76</v>
-      </c>
-      <c r="L281" t="n">
-        <v>2782.955559373141</v>
-      </c>
-      <c r="M281" t="n">
-        <v>2607.085011948757</v>
-      </c>
-      <c r="N281" t="n">
-        <v>83.98837288254001</v>
-      </c>
-      <c r="O281" t="n">
-        <v>2384.207646674</v>
-      </c>
-      <c r="P281" t="n">
-        <v>4921.03817688</v>
-      </c>
-      <c r="Q281" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R281" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S281" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T281" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B282" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C282" t="n">
-        <v>10</v>
-      </c>
-      <c r="D282" t="n">
-        <v>7.853307313798277</v>
-      </c>
-      <c r="E282" t="n">
-        <v>9.591210385276415</v>
-      </c>
-      <c r="F282" t="n">
-        <v>14</v>
-      </c>
-      <c r="G282" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H282" t="n">
-        <v>0.08710379011183118</v>
-      </c>
-      <c r="I282" t="n">
-        <v>14</v>
-      </c>
-      <c r="J282" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K282" t="n">
-        <v>3997.56</v>
-      </c>
-      <c r="L282" t="n">
-        <v>15629.01998012371</v>
-      </c>
-      <c r="M282" t="n">
-        <v>6487.550128401559</v>
-      </c>
-      <c r="N282" t="n">
-        <v>741.7082303399999</v>
-      </c>
-      <c r="O282" t="n">
-        <v>7106.6838794</v>
-      </c>
-      <c r="P282" t="n">
-        <v>28533.419418</v>
-      </c>
-      <c r="Q282" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R282" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S282" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T282" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B283" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C283" t="n">
-        <v>4</v>
-      </c>
-      <c r="D283" t="n">
-        <v>2.191637000866565</v>
-      </c>
-      <c r="E283" t="n">
-        <v>9.293565808940587</v>
-      </c>
-      <c r="F283" t="n">
-        <v>14</v>
-      </c>
-      <c r="G283" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H283" t="n">
-        <v>0.1742075802236624</v>
-      </c>
-      <c r="I283" t="n">
-        <v>14</v>
-      </c>
-      <c r="J283" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K283" t="n">
-        <v>2891.56</v>
-      </c>
-      <c r="L283" t="n">
-        <v>11761.96926324595</v>
-      </c>
-      <c r="M283" t="n">
-        <v>5319.413731221542</v>
-      </c>
-      <c r="N283" t="n">
-        <v>374.4457123995</v>
-      </c>
-      <c r="O283" t="n">
-        <v>4606.35457485</v>
-      </c>
-      <c r="P283" t="n">
-        <v>16031.772862</v>
-      </c>
-      <c r="Q283" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R283" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S283" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T283" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B284" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C284" t="n">
-        <v>14</v>
-      </c>
-      <c r="D284" t="n">
-        <v>2.267196720079541</v>
-      </c>
-      <c r="E284" t="n">
-        <v>9.856935437888509</v>
-      </c>
-      <c r="F284" t="n">
-        <v>14</v>
-      </c>
-      <c r="G284" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H284" t="n">
-        <v>0.8710379011183119</v>
-      </c>
-      <c r="I284" t="n">
-        <v>14</v>
-      </c>
-      <c r="J284" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K284" t="n">
-        <v>2006.76</v>
-      </c>
-      <c r="L284" t="n">
-        <v>2782.955559373141</v>
-      </c>
-      <c r="M284" t="n">
-        <v>2607.085011948757</v>
-      </c>
-      <c r="N284" t="n">
-        <v>83.98837288254001</v>
-      </c>
-      <c r="O284" t="n">
-        <v>2384.207646674</v>
-      </c>
-      <c r="P284" t="n">
-        <v>4921.03817688</v>
-      </c>
-      <c r="Q284" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R284" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S284" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T284" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B285" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C285" t="n">
-        <v>4</v>
-      </c>
-      <c r="D285" t="n">
-        <v>0.6477704914512973</v>
-      </c>
-      <c r="E285" t="n">
-        <v>9.856935437888509</v>
-      </c>
-      <c r="F285" t="n">
-        <v>14</v>
-      </c>
-      <c r="G285" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H285" t="n">
-        <v>0.8710379011183119</v>
-      </c>
-      <c r="I285" t="n">
-        <v>14</v>
-      </c>
-      <c r="J285" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K285" t="n">
-        <v>2006.76</v>
-      </c>
-      <c r="L285" t="n">
-        <v>2782.955559373141</v>
-      </c>
-      <c r="M285" t="n">
-        <v>2607.085011948757</v>
-      </c>
-      <c r="N285" t="n">
-        <v>83.98837288254001</v>
-      </c>
-      <c r="O285" t="n">
-        <v>2384.207646674</v>
-      </c>
-      <c r="P285" t="n">
-        <v>4921.03817688</v>
-      </c>
-      <c r="Q285" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R285" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S285" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T285" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B286" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C286" t="n">
-        <v>6</v>
-      </c>
-      <c r="D286" t="n">
-        <v>0.9716557371769459</v>
-      </c>
-      <c r="E286" t="n">
-        <v>9.856935437888509</v>
-      </c>
-      <c r="F286" t="n">
-        <v>14</v>
-      </c>
-      <c r="G286" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H286" t="n">
-        <v>0.8710379011183119</v>
-      </c>
-      <c r="I286" t="n">
-        <v>14</v>
-      </c>
-      <c r="J286" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K286" t="n">
-        <v>2006.76</v>
-      </c>
-      <c r="L286" t="n">
-        <v>2782.955559373141</v>
-      </c>
-      <c r="M286" t="n">
-        <v>2607.085011948757</v>
-      </c>
-      <c r="N286" t="n">
-        <v>83.98837288254001</v>
-      </c>
-      <c r="O286" t="n">
-        <v>2384.207646674</v>
-      </c>
-      <c r="P286" t="n">
-        <v>4921.03817688</v>
-      </c>
-      <c r="Q286" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R286" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S286" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T286" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B287" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C287" t="n">
-        <v>2</v>
-      </c>
-      <c r="D287" t="n">
-        <v>1.570661462759655</v>
-      </c>
-      <c r="E287" t="n">
-        <v>9.591210385276415</v>
-      </c>
-      <c r="F287" t="n">
-        <v>14</v>
-      </c>
-      <c r="G287" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H287" t="n">
-        <v>0.08710379011183118</v>
-      </c>
-      <c r="I287" t="n">
-        <v>14</v>
-      </c>
-      <c r="J287" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K287" t="n">
-        <v>3997.56</v>
-      </c>
-      <c r="L287" t="n">
-        <v>15629.01998012371</v>
-      </c>
-      <c r="M287" t="n">
-        <v>6487.550128401559</v>
-      </c>
-      <c r="N287" t="n">
-        <v>741.7082303399999</v>
-      </c>
-      <c r="O287" t="n">
-        <v>7106.6838794</v>
-      </c>
-      <c r="P287" t="n">
-        <v>28533.419418</v>
-      </c>
-      <c r="Q287" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R287" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S287" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T287" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B288" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C288" t="n">
-        <v>6</v>
-      </c>
-      <c r="D288" t="n">
-        <v>3.287455501299847</v>
-      </c>
-      <c r="E288" t="n">
-        <v>9.293565808940587</v>
-      </c>
-      <c r="F288" t="n">
-        <v>14</v>
-      </c>
-      <c r="G288" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H288" t="n">
-        <v>0.1742075802236624</v>
-      </c>
-      <c r="I288" t="n">
-        <v>14</v>
-      </c>
-      <c r="J288" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K288" t="n">
-        <v>2891.56</v>
-      </c>
-      <c r="L288" t="n">
-        <v>11761.96926324595</v>
-      </c>
-      <c r="M288" t="n">
-        <v>5319.413731221542</v>
-      </c>
-      <c r="N288" t="n">
-        <v>374.4457123995</v>
-      </c>
-      <c r="O288" t="n">
-        <v>4606.35457485</v>
-      </c>
-      <c r="P288" t="n">
-        <v>16031.772862</v>
-      </c>
-      <c r="Q288" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R288" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S288" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T288" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B289" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C289" t="n">
-        <v>2</v>
-      </c>
-      <c r="D289" t="n">
-        <v>1.095818500433282</v>
-      </c>
-      <c r="E289" t="n">
-        <v>9.293565808940587</v>
-      </c>
-      <c r="F289" t="n">
-        <v>14</v>
-      </c>
-      <c r="G289" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H289" t="n">
-        <v>0.1742075802236624</v>
-      </c>
-      <c r="I289" t="n">
-        <v>14</v>
-      </c>
-      <c r="J289" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K289" t="n">
-        <v>2891.56</v>
-      </c>
-      <c r="L289" t="n">
-        <v>11761.96926324595</v>
-      </c>
-      <c r="M289" t="n">
-        <v>5319.413731221542</v>
-      </c>
-      <c r="N289" t="n">
-        <v>374.4457123995</v>
-      </c>
-      <c r="O289" t="n">
-        <v>4606.35457485</v>
-      </c>
-      <c r="P289" t="n">
-        <v>16031.772862</v>
-      </c>
-      <c r="Q289" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R289" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S289" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T289" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B290" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C290" t="n">
-        <v>6</v>
-      </c>
-      <c r="D290" t="n">
-        <v>4.711984388278966</v>
-      </c>
-      <c r="E290" t="n">
-        <v>9.591210385276415</v>
-      </c>
-      <c r="F290" t="n">
-        <v>14</v>
-      </c>
-      <c r="G290" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H290" t="n">
-        <v>0.08710379011183118</v>
-      </c>
-      <c r="I290" t="n">
-        <v>14</v>
-      </c>
-      <c r="J290" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K290" t="n">
-        <v>3997.56</v>
-      </c>
-      <c r="L290" t="n">
-        <v>15629.01998012371</v>
-      </c>
-      <c r="M290" t="n">
-        <v>6487.550128401559</v>
-      </c>
-      <c r="N290" t="n">
-        <v>741.7082303399999</v>
-      </c>
-      <c r="O290" t="n">
-        <v>7106.6838794</v>
-      </c>
-      <c r="P290" t="n">
-        <v>28533.419418</v>
-      </c>
-      <c r="Q290" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R290" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S290" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T290" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B291" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C291" t="n">
-        <v>4</v>
-      </c>
-      <c r="D291" t="n">
-        <v>3.141322925519311</v>
-      </c>
-      <c r="E291" t="n">
-        <v>9.591210385276415</v>
-      </c>
-      <c r="F291" t="n">
-        <v>14</v>
-      </c>
-      <c r="G291" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H291" t="n">
-        <v>0.08710379011183118</v>
-      </c>
-      <c r="I291" t="n">
-        <v>14</v>
-      </c>
-      <c r="J291" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K291" t="n">
-        <v>3997.56</v>
-      </c>
-      <c r="L291" t="n">
-        <v>15629.01998012371</v>
-      </c>
-      <c r="M291" t="n">
-        <v>6487.550128401559</v>
-      </c>
-      <c r="N291" t="n">
-        <v>741.7082303399999</v>
-      </c>
-      <c r="O291" t="n">
-        <v>7106.6838794</v>
-      </c>
-      <c r="P291" t="n">
-        <v>28533.419418</v>
-      </c>
-      <c r="Q291" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R291" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S291" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T291" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B292" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C292" t="n">
-        <v>10</v>
-      </c>
-      <c r="D292" t="n">
-        <v>1.619426228628243</v>
-      </c>
-      <c r="E292" t="n">
-        <v>9.856935437888509</v>
-      </c>
-      <c r="F292" t="n">
-        <v>14</v>
-      </c>
-      <c r="G292" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H292" t="n">
-        <v>0.8710379011183119</v>
-      </c>
-      <c r="I292" t="n">
-        <v>14</v>
-      </c>
-      <c r="J292" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K292" t="n">
-        <v>2006.76</v>
-      </c>
-      <c r="L292" t="n">
-        <v>2782.955559373141</v>
-      </c>
-      <c r="M292" t="n">
-        <v>2607.085011948757</v>
-      </c>
-      <c r="N292" t="n">
-        <v>83.98837288254001</v>
-      </c>
-      <c r="O292" t="n">
-        <v>2384.207646674</v>
-      </c>
-      <c r="P292" t="n">
-        <v>4921.03817688</v>
-      </c>
-      <c r="Q292" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R292" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S292" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T292" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B293" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C293" t="n">
-        <v>14</v>
-      </c>
-      <c r="D293" t="n">
-        <v>10.99463023931759</v>
-      </c>
-      <c r="E293" t="n">
-        <v>9.591210385276415</v>
-      </c>
-      <c r="F293" t="n">
-        <v>14</v>
-      </c>
-      <c r="G293" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H293" t="n">
-        <v>0.08710379011183118</v>
-      </c>
-      <c r="I293" t="n">
-        <v>14</v>
-      </c>
-      <c r="J293" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K293" t="n">
-        <v>3997.56</v>
-      </c>
-      <c r="L293" t="n">
-        <v>15629.01998012371</v>
-      </c>
-      <c r="M293" t="n">
-        <v>6487.550128401559</v>
-      </c>
-      <c r="N293" t="n">
-        <v>741.7082303399999</v>
-      </c>
-      <c r="O293" t="n">
-        <v>7106.6838794</v>
-      </c>
-      <c r="P293" t="n">
-        <v>28533.419418</v>
-      </c>
-      <c r="Q293" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R293" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S293" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T293" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B294" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C294" t="n">
-        <v>14</v>
-      </c>
-      <c r="D294" t="n">
-        <v>7.670729503032977</v>
-      </c>
-      <c r="E294" t="n">
-        <v>9.293565808940587</v>
-      </c>
-      <c r="F294" t="n">
-        <v>14</v>
-      </c>
-      <c r="G294" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H294" t="n">
-        <v>0.1742075802236624</v>
-      </c>
-      <c r="I294" t="n">
-        <v>14</v>
-      </c>
-      <c r="J294" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K294" t="n">
-        <v>2891.56</v>
-      </c>
-      <c r="L294" t="n">
-        <v>11761.96926324595</v>
-      </c>
-      <c r="M294" t="n">
-        <v>5319.413731221542</v>
-      </c>
-      <c r="N294" t="n">
-        <v>374.4457123995</v>
-      </c>
-      <c r="O294" t="n">
-        <v>4606.35457485</v>
-      </c>
-      <c r="P294" t="n">
-        <v>16031.772862</v>
-      </c>
-      <c r="Q294" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R294" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S294" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T294" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B295" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C295" t="n">
-        <v>2</v>
-      </c>
-      <c r="D295" t="n">
-        <v>1.856513018878587</v>
-      </c>
-      <c r="E295" t="n">
-        <v>10.0402636072274</v>
-      </c>
-      <c r="F295" t="n">
-        <v>14</v>
-      </c>
-      <c r="G295" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H295" t="n">
-        <v>0.04355189505591559</v>
-      </c>
-      <c r="I295" t="n">
-        <v>14</v>
-      </c>
-      <c r="J295" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K295" t="n">
-        <v>6209.560000000001</v>
-      </c>
-      <c r="L295" t="n">
-        <v>19496.07069700147</v>
-      </c>
-      <c r="M295" t="n">
-        <v>7655.686525581573</v>
-      </c>
-      <c r="N295" t="n">
-        <v>1490.202744702</v>
-      </c>
-      <c r="O295" t="n">
-        <v>11182.8279696</v>
-      </c>
-      <c r="P295" t="n">
-        <v>48914.13986199999</v>
-      </c>
-      <c r="Q295" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R295" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S295" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T295" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B296" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C296" t="n">
-        <v>6</v>
-      </c>
-      <c r="D296" t="n">
-        <v>5.569539056635763</v>
-      </c>
-      <c r="E296" t="n">
-        <v>10.0402636072274</v>
-      </c>
-      <c r="F296" t="n">
-        <v>14</v>
-      </c>
-      <c r="G296" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H296" t="n">
-        <v>0.04355189505591559</v>
-      </c>
-      <c r="I296" t="n">
-        <v>14</v>
-      </c>
-      <c r="J296" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K296" t="n">
-        <v>6209.560000000001</v>
-      </c>
-      <c r="L296" t="n">
-        <v>19496.07069700147</v>
-      </c>
-      <c r="M296" t="n">
-        <v>7655.686525581573</v>
-      </c>
-      <c r="N296" t="n">
-        <v>1490.202744702</v>
-      </c>
-      <c r="O296" t="n">
-        <v>11182.8279696</v>
-      </c>
-      <c r="P296" t="n">
-        <v>48914.13986199999</v>
-      </c>
-      <c r="Q296" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R296" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S296" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T296" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B297" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C297" t="n">
-        <v>10</v>
-      </c>
-      <c r="D297" t="n">
-        <v>5.479092502166411</v>
-      </c>
-      <c r="E297" t="n">
-        <v>9.293565808940587</v>
-      </c>
-      <c r="F297" t="n">
-        <v>14</v>
-      </c>
-      <c r="G297" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H297" t="n">
-        <v>0.1742075802236624</v>
-      </c>
-      <c r="I297" t="n">
-        <v>14</v>
-      </c>
-      <c r="J297" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K297" t="n">
-        <v>2891.56</v>
-      </c>
-      <c r="L297" t="n">
-        <v>11761.96926324595</v>
-      </c>
-      <c r="M297" t="n">
-        <v>5319.413731221542</v>
-      </c>
-      <c r="N297" t="n">
-        <v>374.4457123995</v>
-      </c>
-      <c r="O297" t="n">
-        <v>4606.35457485</v>
-      </c>
-      <c r="P297" t="n">
-        <v>16031.772862</v>
-      </c>
-      <c r="Q297" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R297" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S297" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T297" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B298" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C298" t="n">
-        <v>4</v>
-      </c>
-      <c r="D298" t="n">
-        <v>3.713026037757175</v>
-      </c>
-      <c r="E298" t="n">
-        <v>10.0402636072274</v>
-      </c>
-      <c r="F298" t="n">
-        <v>14</v>
-      </c>
-      <c r="G298" t="n">
-        <v>7630.292013796412</v>
-      </c>
-      <c r="H298" t="n">
-        <v>0.04355189505591559</v>
-      </c>
-      <c r="I298" t="n">
-        <v>14</v>
-      </c>
-      <c r="J298" t="n">
-        <v>23.15734126984127</v>
-      </c>
-      <c r="K298" t="n">
-        <v>6209.560000000001</v>
-      </c>
-      <c r="L298" t="n">
-        <v>19496.07069700147</v>
-      </c>
-      <c r="M298" t="n">
-        <v>7655.686525581573</v>
-      </c>
-      <c r="N298" t="n">
-        <v>1490.202744702</v>
-      </c>
-      <c r="O298" t="n">
-        <v>11182.8279696</v>
-      </c>
-      <c r="P298" t="n">
-        <v>48914.13986199999</v>
-      </c>
-      <c r="Q298" t="n">
-        <v>1242.01</v>
-      </c>
-      <c r="R298" t="n">
-        <v>1542.52</v>
-      </c>
-      <c r="S298" t="n">
-        <v>350.0350000000004</v>
-      </c>
-      <c r="T298" t="n">
-        <v>3000</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sitkana/Fixed Vessel Cases/Site 1 Optimal/results_df.xlsx
+++ b/sitkana/Fixed Vessel Cases/Site 1 Optimal/results_df.xlsx
@@ -544,7 +544,7 @@
         <v>1.359212070604933</v>
       </c>
       <c r="E2" t="n">
-        <v>66.93422689188083</v>
+        <v>66.90536365754498</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -580,13 +580,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q2" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R2" t="n">
         <v>273.04</v>
       </c>
       <c r="S2" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T2" t="n">
         <v>3000</v>
@@ -606,7 +606,7 @@
         <v>3.947977693021837</v>
       </c>
       <c r="E3" t="n">
-        <v>6.519327143399511</v>
+        <v>6.496325866912001</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -642,13 +642,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>1752.86</v>
+        <v>35.09</v>
       </c>
       <c r="R3" t="n">
         <v>663.05</v>
       </c>
       <c r="S3" t="n">
-        <v>582.83</v>
+        <v>13.09</v>
       </c>
       <c r="T3" t="n">
         <v>3000</v>
@@ -668,7 +668,7 @@
         <v>8.57008404441013</v>
       </c>
       <c r="E4" t="n">
-        <v>26.5891190471558</v>
+        <v>26.56025581281996</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -704,13 +704,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R4" t="n">
         <v>273.04</v>
       </c>
       <c r="S4" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T4" t="n">
         <v>3000</v>
@@ -730,7 +730,7 @@
         <v>3.672484667368295</v>
       </c>
       <c r="E5" t="n">
-        <v>15.3375248445156</v>
+        <v>15.31194156453927</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -766,13 +766,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q5" t="n">
-        <v>1058.145</v>
+        <v>21.195</v>
       </c>
       <c r="R5" t="n">
         <v>457.33</v>
       </c>
       <c r="S5" t="n">
-        <v>400.7925</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>3000</v>
@@ -792,7 +792,7 @@
         <v>12.99559113215011</v>
       </c>
       <c r="E6" t="n">
-        <v>125.0628227973195</v>
+        <v>125.0417754768527</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -828,13 +828,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R6" t="n">
         <v>110.18</v>
       </c>
       <c r="S6" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T6" t="n">
         <v>3000</v>
@@ -854,7 +854,7 @@
         <v>2.281025076512125</v>
       </c>
       <c r="E7" t="n">
-        <v>29.63784221111891</v>
+        <v>29.61184711190975</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -890,13 +890,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q7" t="n">
-        <v>1058.145</v>
+        <v>21.195</v>
       </c>
       <c r="R7" t="n">
         <v>457.33</v>
       </c>
       <c r="S7" t="n">
-        <v>400.7925</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="T7" t="n">
         <v>3000</v>
@@ -916,7 +916,7 @@
         <v>9.862366503899541</v>
       </c>
       <c r="E8" t="n">
-        <v>315.0529841578885</v>
+        <v>315.0319368374218</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -952,13 +952,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q8" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R8" t="n">
         <v>110.18</v>
       </c>
       <c r="S8" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T8" t="n">
         <v>3000</v>
@@ -978,7 +978,7 @@
         <v>9.282565094392938</v>
       </c>
       <c r="E9" t="n">
-        <v>125.0628227973195</v>
+        <v>125.0417754768527</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -1014,13 +1014,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R9" t="n">
         <v>110.18</v>
       </c>
       <c r="S9" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T9" t="n">
         <v>3000</v>
@@ -1040,7 +1040,7 @@
         <v>4.077636211814798</v>
       </c>
       <c r="E10" t="n">
-        <v>66.93422689188083</v>
+        <v>66.90536365754498</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -1076,13 +1076,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q10" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R10" t="n">
         <v>273.04</v>
       </c>
       <c r="S10" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T10" t="n">
         <v>3000</v>
@@ -1102,7 +1102,7 @@
         <v>6.121488603150093</v>
       </c>
       <c r="E11" t="n">
-        <v>26.5891190471558</v>
+        <v>26.56025581281996</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -1138,13 +1138,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R11" t="n">
         <v>273.04</v>
       </c>
       <c r="S11" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T11" t="n">
         <v>3000</v>
@@ -1164,7 +1164,7 @@
         <v>4.854950889965759</v>
       </c>
       <c r="E12" t="n">
-        <v>11.5968824949234</v>
+        <v>11.57129921494708</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -1200,13 +1200,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>1058.145</v>
+        <v>21.195</v>
       </c>
       <c r="R12" t="n">
         <v>457.33</v>
       </c>
       <c r="S12" t="n">
-        <v>400.7925</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>3000</v>
@@ -1226,7 +1226,7 @@
         <v>14.1359531648369</v>
       </c>
       <c r="E13" t="n">
-        <v>165.5083178021928</v>
+        <v>165.4872704817261</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -1262,13 +1262,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q13" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R13" t="n">
         <v>110.18</v>
       </c>
       <c r="S13" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T13" t="n">
         <v>3000</v>
@@ -1288,7 +1288,7 @@
         <v>6.872523497754584</v>
       </c>
       <c r="E14" t="n">
-        <v>35.17786830721914</v>
+        <v>35.14900507288331</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1324,13 +1324,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q14" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R14" t="n">
         <v>273.04</v>
       </c>
       <c r="S14" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T14" t="n">
         <v>3000</v>
@@ -1350,7 +1350,7 @@
         <v>1.580839825261526</v>
       </c>
       <c r="E15" t="n">
-        <v>194.0380338605753</v>
+        <v>194.0034381620868</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -1386,13 +1386,13 @@
         <v>351.50272692</v>
       </c>
       <c r="Q15" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R15" t="n">
         <v>273.04</v>
       </c>
       <c r="S15" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T15" t="n">
         <v>3000</v>
@@ -1412,7 +1412,7 @@
         <v>2.914967211530838</v>
       </c>
       <c r="E16" t="n">
-        <v>762.1935815126093</v>
+        <v>762.1725341921424</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -1448,13 +1448,13 @@
         <v>351.50272692</v>
       </c>
       <c r="Q16" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R16" t="n">
         <v>110.18</v>
       </c>
       <c r="S16" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T16" t="n">
         <v>3000</v>
@@ -1474,7 +1474,7 @@
         <v>3.467822064261256</v>
       </c>
       <c r="E17" t="n">
-        <v>11.5968824949234</v>
+        <v>11.57129921494708</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -1510,13 +1510,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>1058.145</v>
+        <v>21.195</v>
       </c>
       <c r="R17" t="n">
         <v>457.33</v>
       </c>
       <c r="S17" t="n">
-        <v>400.7925</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="T17" t="n">
         <v>3000</v>
@@ -1536,7 +1536,7 @@
         <v>7.853307313798277</v>
       </c>
       <c r="E18" t="n">
-        <v>165.5083178021928</v>
+        <v>165.4872704817261</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -1572,13 +1572,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q18" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R18" t="n">
         <v>110.18</v>
       </c>
       <c r="S18" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T18" t="n">
         <v>3000</v>
@@ -1598,7 +1598,7 @@
         <v>2.191637000866565</v>
       </c>
       <c r="E19" t="n">
-        <v>315.0529841578885</v>
+        <v>315.0319368374218</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -1634,13 +1634,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q19" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R19" t="n">
         <v>110.18</v>
       </c>
       <c r="S19" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T19" t="n">
         <v>3000</v>
@@ -1660,7 +1660,7 @@
         <v>2.267196720079541</v>
       </c>
       <c r="E20" t="n">
-        <v>762.1935815126093</v>
+        <v>762.1725341921424</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -1696,13 +1696,13 @@
         <v>351.50272692</v>
       </c>
       <c r="Q20" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R20" t="n">
         <v>110.18</v>
       </c>
       <c r="S20" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T20" t="n">
         <v>3000</v>
@@ -1722,7 +1722,7 @@
         <v>0.6477704914512973</v>
       </c>
       <c r="E21" t="n">
-        <v>762.1935815126093</v>
+        <v>762.1725341921424</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -1758,13 +1758,13 @@
         <v>351.50272692</v>
       </c>
       <c r="Q21" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R21" t="n">
         <v>110.18</v>
       </c>
       <c r="S21" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T21" t="n">
         <v>3000</v>
@@ -1784,7 +1784,7 @@
         <v>0.9716557371769459</v>
       </c>
       <c r="E22" t="n">
-        <v>762.1935815126093</v>
+        <v>762.1725341921424</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -1820,13 +1820,13 @@
         <v>351.50272692</v>
       </c>
       <c r="Q22" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R22" t="n">
         <v>110.18</v>
       </c>
       <c r="S22" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T22" t="n">
         <v>3000</v>
@@ -1846,7 +1846,7 @@
         <v>1.22954208631452</v>
       </c>
       <c r="E23" t="n">
-        <v>194.0380338605753</v>
+        <v>194.0034381620868</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -1882,13 +1882,13 @@
         <v>351.50272692</v>
       </c>
       <c r="Q23" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R23" t="n">
         <v>273.04</v>
       </c>
       <c r="S23" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T23" t="n">
         <v>3000</v>
@@ -1908,7 +1908,7 @@
         <v>1.570661462759655</v>
       </c>
       <c r="E24" t="n">
-        <v>165.5083178021928</v>
+        <v>165.4872704817261</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -1944,13 +1944,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q24" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R24" t="n">
         <v>110.18</v>
       </c>
       <c r="S24" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T24" t="n">
         <v>3000</v>
@@ -1970,7 +1970,7 @@
         <v>3.287455501299847</v>
       </c>
       <c r="E25" t="n">
-        <v>315.0529841578885</v>
+        <v>315.0319368374218</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -2006,13 +2006,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q25" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R25" t="n">
         <v>110.18</v>
       </c>
       <c r="S25" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T25" t="n">
         <v>3000</v>
@@ -2032,7 +2032,7 @@
         <v>3.818068609863658</v>
       </c>
       <c r="E26" t="n">
-        <v>35.17786830721914</v>
+        <v>35.14900507288331</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -2068,13 +2068,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q26" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R26" t="n">
         <v>273.04</v>
       </c>
       <c r="S26" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T26" t="n">
         <v>3000</v>
@@ -2094,7 +2094,7 @@
         <v>5.345296053809121</v>
       </c>
       <c r="E27" t="n">
-        <v>35.17786830721914</v>
+        <v>35.14900507288331</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
@@ -2130,13 +2130,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q27" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R27" t="n">
         <v>273.04</v>
       </c>
       <c r="S27" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T27" t="n">
         <v>3000</v>
@@ -2156,7 +2156,7 @@
         <v>1.095818500433282</v>
       </c>
       <c r="E28" t="n">
-        <v>315.0529841578885</v>
+        <v>315.0319368374218</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
@@ -2192,13 +2192,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q28" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R28" t="n">
         <v>110.18</v>
       </c>
       <c r="S28" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T28" t="n">
         <v>3000</v>
@@ -2218,7 +2218,7 @@
         <v>2.391486505666307</v>
       </c>
       <c r="E29" t="n">
-        <v>8.678594481194006</v>
+        <v>8.655433262240768</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
@@ -2254,13 +2254,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q29" t="n">
-        <v>1752.86</v>
+        <v>35.09</v>
       </c>
       <c r="R29" t="n">
         <v>663.05</v>
       </c>
       <c r="S29" t="n">
-        <v>582.83</v>
+        <v>13.09</v>
       </c>
       <c r="T29" t="n">
         <v>3000</v>
@@ -2280,7 +2280,7 @@
         <v>1.527227443945463</v>
       </c>
       <c r="E30" t="n">
-        <v>35.17786830721914</v>
+        <v>35.14900507288331</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
@@ -2316,13 +2316,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q30" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R30" t="n">
         <v>273.04</v>
       </c>
       <c r="S30" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T30" t="n">
         <v>3000</v>
@@ -2342,7 +2342,7 @@
         <v>4.711984388278966</v>
       </c>
       <c r="E31" t="n">
-        <v>165.5083178021928</v>
+        <v>165.4872704817261</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
@@ -2378,13 +2378,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q31" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R31" t="n">
         <v>110.18</v>
       </c>
       <c r="S31" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T31" t="n">
         <v>3000</v>
@@ -2404,7 +2404,7 @@
         <v>3.141322925519311</v>
       </c>
       <c r="E32" t="n">
-        <v>165.5083178021928</v>
+        <v>165.4872704817261</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
@@ -2440,13 +2440,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q32" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R32" t="n">
         <v>110.18</v>
       </c>
       <c r="S32" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T32" t="n">
         <v>3000</v>
@@ -2466,7 +2466,7 @@
         <v>1.619426228628243</v>
       </c>
       <c r="E33" t="n">
-        <v>762.1935815126093</v>
+        <v>762.1725341921424</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
@@ -2502,13 +2502,13 @@
         <v>351.50272692</v>
       </c>
       <c r="Q33" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R33" t="n">
         <v>110.18</v>
       </c>
       <c r="S33" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T33" t="n">
         <v>3000</v>
@@ -2528,7 +2528,7 @@
         <v>2.290841165918195</v>
       </c>
       <c r="E34" t="n">
-        <v>35.17786830721914</v>
+        <v>35.14900507288331</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
@@ -2564,13 +2564,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q34" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R34" t="n">
         <v>273.04</v>
       </c>
       <c r="S34" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T34" t="n">
         <v>3000</v>
@@ -2590,7 +2590,7 @@
         <v>10.99463023931759</v>
       </c>
       <c r="E35" t="n">
-        <v>165.5083178021928</v>
+        <v>165.4872704817261</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
@@ -2626,13 +2626,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q35" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R35" t="n">
         <v>110.18</v>
       </c>
       <c r="S35" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T35" t="n">
         <v>3000</v>
@@ -2652,7 +2652,7 @@
         <v>6.242079715670261</v>
       </c>
       <c r="E36" t="n">
-        <v>11.5968824949234</v>
+        <v>11.57129921494708</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
@@ -2688,13 +2688,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q36" t="n">
-        <v>1058.145</v>
+        <v>21.195</v>
       </c>
       <c r="R36" t="n">
         <v>457.33</v>
       </c>
       <c r="S36" t="n">
-        <v>400.7925</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="T36" t="n">
         <v>3000</v>
@@ -2714,7 +2714,7 @@
         <v>1.224297720630019</v>
       </c>
       <c r="E37" t="n">
-        <v>26.5891190471558</v>
+        <v>26.56025581281996</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
@@ -2750,13 +2750,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q37" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R37" t="n">
         <v>273.04</v>
       </c>
       <c r="S37" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T37" t="n">
         <v>3000</v>
@@ -2776,7 +2776,7 @@
         <v>3.171494831411509</v>
       </c>
       <c r="E38" t="n">
-        <v>66.93422689188083</v>
+        <v>66.90536365754498</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
@@ -2812,13 +2812,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q38" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R38" t="n">
         <v>273.04</v>
       </c>
       <c r="S38" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T38" t="n">
         <v>3000</v>
@@ -2838,7 +2838,7 @@
         <v>2.193320940567687</v>
       </c>
       <c r="E39" t="n">
-        <v>6.519327143399511</v>
+        <v>6.496325866912001</v>
       </c>
       <c r="F39" t="n">
         <v>1</v>
@@ -2874,13 +2874,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q39" t="n">
-        <v>1752.86</v>
+        <v>35.09</v>
       </c>
       <c r="R39" t="n">
         <v>663.05</v>
       </c>
       <c r="S39" t="n">
-        <v>582.83</v>
+        <v>13.09</v>
       </c>
       <c r="T39" t="n">
         <v>3000</v>
@@ -2900,7 +2900,7 @@
         <v>2.040269259649053</v>
       </c>
       <c r="E40" t="n">
-        <v>15.3375248445156</v>
+        <v>15.31194156453927</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
@@ -2936,13 +2936,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q40" t="n">
-        <v>1058.145</v>
+        <v>21.195</v>
       </c>
       <c r="R40" t="n">
         <v>457.33</v>
       </c>
       <c r="S40" t="n">
-        <v>400.7925</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="T40" t="n">
         <v>3000</v>
@@ -2962,7 +2962,7 @@
         <v>7.670729503032977</v>
       </c>
       <c r="E41" t="n">
-        <v>315.0529841578885</v>
+        <v>315.0319368374218</v>
       </c>
       <c r="F41" t="n">
         <v>1</v>
@@ -2998,13 +2998,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q41" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R41" t="n">
         <v>110.18</v>
       </c>
       <c r="S41" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T41" t="n">
         <v>3000</v>
@@ -3024,7 +3024,7 @@
         <v>1.856513018878587</v>
       </c>
       <c r="E42" t="n">
-        <v>125.0628227973195</v>
+        <v>125.0417754768527</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
@@ -3060,13 +3060,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q42" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R42" t="n">
         <v>110.18</v>
       </c>
       <c r="S42" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T42" t="n">
         <v>3000</v>
@@ -3086,7 +3086,7 @@
         <v>1.774130615064986</v>
       </c>
       <c r="E43" t="n">
-        <v>29.63784221111891</v>
+        <v>29.61184711190975</v>
       </c>
       <c r="F43" t="n">
         <v>1</v>
@@ -3122,13 +3122,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q43" t="n">
-        <v>1058.145</v>
+        <v>21.195</v>
       </c>
       <c r="R43" t="n">
         <v>457.33</v>
       </c>
       <c r="S43" t="n">
-        <v>400.7925</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="T43" t="n">
         <v>3000</v>
@@ -3148,7 +3148,7 @@
         <v>5.569539056635763</v>
       </c>
       <c r="E44" t="n">
-        <v>125.0628227973195</v>
+        <v>125.0417754768527</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
@@ -3184,13 +3184,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q44" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R44" t="n">
         <v>110.18</v>
       </c>
       <c r="S44" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T44" t="n">
         <v>3000</v>
@@ -3210,7 +3210,7 @@
         <v>2.448595441260037</v>
       </c>
       <c r="E45" t="n">
-        <v>26.5891190471558</v>
+        <v>26.56025581281996</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
@@ -3246,13 +3246,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q45" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R45" t="n">
         <v>273.04</v>
       </c>
       <c r="S45" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T45" t="n">
         <v>3000</v>
@@ -3272,7 +3272,7 @@
         <v>16.70861716990729</v>
       </c>
       <c r="E46" t="n">
-        <v>125.0628227973195</v>
+        <v>125.0417754768527</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
@@ -3308,13 +3308,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q46" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R46" t="n">
         <v>110.18</v>
       </c>
       <c r="S46" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T46" t="n">
         <v>3000</v>
@@ -3334,7 +3334,7 @@
         <v>2.080693238556754</v>
       </c>
       <c r="E47" t="n">
-        <v>11.5968824949234</v>
+        <v>11.57129921494708</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
@@ -3370,13 +3370,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q47" t="n">
-        <v>1058.145</v>
+        <v>21.195</v>
       </c>
       <c r="R47" t="n">
         <v>457.33</v>
       </c>
       <c r="S47" t="n">
-        <v>400.7925</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="T47" t="n">
         <v>3000</v>
@@ -3396,7 +3396,7 @@
         <v>2.856376963508674</v>
       </c>
       <c r="E48" t="n">
-        <v>15.3375248445156</v>
+        <v>15.31194156453927</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
@@ -3432,13 +3432,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q48" t="n">
-        <v>1058.145</v>
+        <v>21.195</v>
       </c>
       <c r="R48" t="n">
         <v>457.33</v>
       </c>
       <c r="S48" t="n">
-        <v>400.7925</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="T48" t="n">
         <v>3000</v>
@@ -3458,7 +3458,7 @@
         <v>5.479092502166411</v>
       </c>
       <c r="E49" t="n">
-        <v>315.0529841578885</v>
+        <v>315.0319368374218</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
@@ -3494,13 +3494,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q49" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R49" t="n">
         <v>110.18</v>
       </c>
       <c r="S49" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T49" t="n">
         <v>3000</v>
@@ -3520,7 +3520,7 @@
         <v>11.01867948567017</v>
       </c>
       <c r="E50" t="n">
-        <v>26.5891190471558</v>
+        <v>26.56025581281996</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
@@ -3556,13 +3556,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q50" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R50" t="n">
         <v>273.04</v>
       </c>
       <c r="S50" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T50" t="n">
         <v>3000</v>
@@ -3582,7 +3582,7 @@
         <v>3.070649316794762</v>
       </c>
       <c r="E51" t="n">
-        <v>6.519327143399511</v>
+        <v>6.496325866912001</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
@@ -3618,13 +3618,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q51" t="n">
-        <v>1752.86</v>
+        <v>35.09</v>
       </c>
       <c r="R51" t="n">
         <v>663.05</v>
       </c>
       <c r="S51" t="n">
-        <v>582.83</v>
+        <v>13.09</v>
       </c>
       <c r="T51" t="n">
         <v>3000</v>
@@ -3644,7 +3644,7 @@
         <v>2.265353451008221</v>
       </c>
       <c r="E52" t="n">
-        <v>66.93422689188083</v>
+        <v>66.90536365754498</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
@@ -3680,13 +3680,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q52" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R52" t="n">
         <v>273.04</v>
       </c>
       <c r="S52" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T52" t="n">
         <v>3000</v>
@@ -3706,7 +3706,7 @@
         <v>3.672893161890055</v>
       </c>
       <c r="E53" t="n">
-        <v>26.5891190471558</v>
+        <v>26.56025581281996</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
@@ -3742,13 +3742,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q53" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R53" t="n">
         <v>273.04</v>
       </c>
       <c r="S53" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T53" t="n">
         <v>3000</v>
@@ -3768,7 +3768,7 @@
         <v>3.713026037757175</v>
       </c>
       <c r="E54" t="n">
-        <v>125.0628227973195</v>
+        <v>125.0417754768527</v>
       </c>
       <c r="F54" t="n">
         <v>1</v>
@@ -3804,13 +3804,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q54" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R54" t="n">
         <v>110.18</v>
       </c>
       <c r="S54" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T54" t="n">
         <v>3000</v>
@@ -3830,7 +3830,7 @@
         <v>1.359212070604933</v>
       </c>
       <c r="E55" t="n">
-        <v>17.63793698200517</v>
+        <v>17.60907374766933</v>
       </c>
       <c r="F55" t="n">
         <v>2</v>
@@ -3866,13 +3866,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q55" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R55" t="n">
         <v>546.08</v>
       </c>
       <c r="S55" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T55" t="n">
         <v>3000</v>
@@ -3892,7 +3892,7 @@
         <v>3.947977693021837</v>
       </c>
       <c r="E56" t="n">
-        <v>3.25336631452332</v>
+        <v>3.230365038035811</v>
       </c>
       <c r="F56" t="n">
         <v>2</v>
@@ -3928,13 +3928,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q56" t="n">
-        <v>3505.72</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="R56" t="n">
         <v>1326.1</v>
       </c>
       <c r="S56" t="n">
-        <v>1165.66</v>
+        <v>26.18</v>
       </c>
       <c r="T56" t="n">
         <v>3000</v>
@@ -3954,7 +3954,7 @@
         <v>8.57008404441013</v>
       </c>
       <c r="E57" t="n">
-        <v>13.2275063309872</v>
+        <v>13.19864309665136</v>
       </c>
       <c r="F57" t="n">
         <v>2</v>
@@ -3990,13 +3990,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q57" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R57" t="n">
         <v>546.08</v>
       </c>
       <c r="S57" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T57" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>3.672484667368295</v>
       </c>
       <c r="E58" t="n">
-        <v>5.83483166290713</v>
+        <v>5.809248382930803</v>
       </c>
       <c r="F58" t="n">
         <v>2</v>
@@ -4052,13 +4052,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q58" t="n">
-        <v>2116.29</v>
+        <v>42.39</v>
       </c>
       <c r="R58" t="n">
         <v>914.66</v>
       </c>
       <c r="S58" t="n">
-        <v>801.585</v>
+        <v>19.65</v>
       </c>
       <c r="T58" t="n">
         <v>3000</v>
@@ -4078,7 +4078,7 @@
         <v>12.99559113215011</v>
       </c>
       <c r="E59" t="n">
-        <v>62.14131653310422</v>
+        <v>62.12026921263746</v>
       </c>
       <c r="F59" t="n">
         <v>2</v>
@@ -4114,13 +4114,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q59" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R59" t="n">
         <v>220.36</v>
       </c>
       <c r="S59" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T59" t="n">
         <v>3000</v>
@@ -4140,7 +4140,7 @@
         <v>2.281025076512125</v>
       </c>
       <c r="E60" t="n">
-        <v>7.82231299292982</v>
+        <v>7.796317893720655</v>
       </c>
       <c r="F60" t="n">
         <v>2</v>
@@ -4176,13 +4176,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q60" t="n">
-        <v>2116.29</v>
+        <v>42.39</v>
       </c>
       <c r="R60" t="n">
         <v>914.66</v>
       </c>
       <c r="S60" t="n">
-        <v>801.585</v>
+        <v>19.65</v>
       </c>
       <c r="T60" t="n">
         <v>3000</v>
@@ -4202,7 +4202,7 @@
         <v>9.862366503899541</v>
       </c>
       <c r="E61" t="n">
-        <v>82.91058636084767</v>
+        <v>82.88953904038092</v>
       </c>
       <c r="F61" t="n">
         <v>2</v>
@@ -4238,13 +4238,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q61" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R61" t="n">
         <v>220.36</v>
       </c>
       <c r="S61" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T61" t="n">
         <v>3000</v>
@@ -4264,7 +4264,7 @@
         <v>9.282565094392938</v>
       </c>
       <c r="E62" t="n">
-        <v>62.14131653310422</v>
+        <v>62.12026921263746</v>
       </c>
       <c r="F62" t="n">
         <v>2</v>
@@ -4300,13 +4300,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q62" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R62" t="n">
         <v>220.36</v>
       </c>
       <c r="S62" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T62" t="n">
         <v>3000</v>
@@ -4326,7 +4326,7 @@
         <v>4.077636211814798</v>
       </c>
       <c r="E63" t="n">
-        <v>17.63793698200517</v>
+        <v>17.60907374766933</v>
       </c>
       <c r="F63" t="n">
         <v>2</v>
@@ -4362,13 +4362,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q63" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R63" t="n">
         <v>546.08</v>
       </c>
       <c r="S63" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T63" t="n">
         <v>3000</v>
@@ -4388,7 +4388,7 @@
         <v>6.121488603150093</v>
       </c>
       <c r="E64" t="n">
-        <v>13.2275063309872</v>
+        <v>13.19864309665136</v>
       </c>
       <c r="F64" t="n">
         <v>2</v>
@@ -4424,13 +4424,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q64" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R64" t="n">
         <v>546.08</v>
       </c>
       <c r="S64" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T64" t="n">
         <v>3000</v>
@@ -4450,7 +4450,7 @@
         <v>4.854950889965759</v>
       </c>
       <c r="E65" t="n">
-        <v>5.777523602080223</v>
+        <v>5.751940322103896</v>
       </c>
       <c r="F65" t="n">
         <v>2</v>
@@ -4486,13 +4486,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q65" t="n">
-        <v>2116.29</v>
+        <v>42.39</v>
       </c>
       <c r="R65" t="n">
         <v>914.66</v>
       </c>
       <c r="S65" t="n">
-        <v>801.585</v>
+        <v>19.65</v>
       </c>
       <c r="T65" t="n">
         <v>3000</v>
@@ -4512,7 +4512,7 @@
         <v>14.1359531648369</v>
       </c>
       <c r="E66" t="n">
-        <v>62.76095687058967</v>
+        <v>62.7399095501229</v>
       </c>
       <c r="F66" t="n">
         <v>2</v>
@@ -4548,13 +4548,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q66" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R66" t="n">
         <v>220.36</v>
       </c>
       <c r="S66" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T66" t="n">
         <v>3000</v>
@@ -4574,7 +4574,7 @@
         <v>6.872523497754584</v>
       </c>
       <c r="E67" t="n">
-        <v>13.35908923013189</v>
+        <v>13.33022599579605</v>
       </c>
       <c r="F67" t="n">
         <v>2</v>
@@ -4610,13 +4610,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q67" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R67" t="n">
         <v>546.08</v>
       </c>
       <c r="S67" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T67" t="n">
         <v>3000</v>
@@ -4636,7 +4636,7 @@
         <v>1.580839825261526</v>
       </c>
       <c r="E68" t="n">
-        <v>75.94672192951562</v>
+        <v>75.91212623102716</v>
       </c>
       <c r="F68" t="n">
         <v>2</v>
@@ -4672,13 +4672,13 @@
         <v>703.00545384</v>
       </c>
       <c r="Q68" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R68" t="n">
         <v>546.08</v>
       </c>
       <c r="S68" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T68" t="n">
         <v>3000</v>
@@ -4698,7 +4698,7 @@
         <v>2.914967211530838</v>
       </c>
       <c r="E69" t="n">
-        <v>298.2330148341655</v>
+        <v>298.2119675136988</v>
       </c>
       <c r="F69" t="n">
         <v>2</v>
@@ -4734,13 +4734,13 @@
         <v>703.00545384</v>
       </c>
       <c r="Q69" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R69" t="n">
         <v>220.36</v>
       </c>
       <c r="S69" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T69" t="n">
         <v>3000</v>
@@ -4760,7 +4760,7 @@
         <v>3.467822064261256</v>
       </c>
       <c r="E70" t="n">
-        <v>5.777523602080223</v>
+        <v>5.751940322103896</v>
       </c>
       <c r="F70" t="n">
         <v>2</v>
@@ -4796,13 +4796,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q70" t="n">
-        <v>2116.29</v>
+        <v>42.39</v>
       </c>
       <c r="R70" t="n">
         <v>914.66</v>
       </c>
       <c r="S70" t="n">
-        <v>801.585</v>
+        <v>19.65</v>
       </c>
       <c r="T70" t="n">
         <v>3000</v>
@@ -4822,7 +4822,7 @@
         <v>7.853307313798277</v>
       </c>
       <c r="E71" t="n">
-        <v>62.76095687058967</v>
+        <v>62.7399095501229</v>
       </c>
       <c r="F71" t="n">
         <v>2</v>
@@ -4858,13 +4858,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q71" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R71" t="n">
         <v>220.36</v>
       </c>
       <c r="S71" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T71" t="n">
         <v>3000</v>
@@ -4884,7 +4884,7 @@
         <v>2.191637000866565</v>
       </c>
       <c r="E72" t="n">
-        <v>82.91058636084767</v>
+        <v>82.88953904038092</v>
       </c>
       <c r="F72" t="n">
         <v>2</v>
@@ -4920,13 +4920,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q72" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R72" t="n">
         <v>220.36</v>
       </c>
       <c r="S72" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T72" t="n">
         <v>3000</v>
@@ -4946,7 +4946,7 @@
         <v>2.267196720079541</v>
       </c>
       <c r="E73" t="n">
-        <v>298.2330148341655</v>
+        <v>298.2119675136988</v>
       </c>
       <c r="F73" t="n">
         <v>2</v>
@@ -4982,13 +4982,13 @@
         <v>703.00545384</v>
       </c>
       <c r="Q73" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R73" t="n">
         <v>220.36</v>
       </c>
       <c r="S73" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T73" t="n">
         <v>3000</v>
@@ -5008,7 +5008,7 @@
         <v>0.6477704914512973</v>
       </c>
       <c r="E74" t="n">
-        <v>298.2330148341655</v>
+        <v>298.2119675136988</v>
       </c>
       <c r="F74" t="n">
         <v>2</v>
@@ -5044,13 +5044,13 @@
         <v>703.00545384</v>
       </c>
       <c r="Q74" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R74" t="n">
         <v>220.36</v>
       </c>
       <c r="S74" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T74" t="n">
         <v>3000</v>
@@ -5070,7 +5070,7 @@
         <v>0.9716557371769459</v>
       </c>
       <c r="E75" t="n">
-        <v>298.2330148341655</v>
+        <v>298.2119675136988</v>
       </c>
       <c r="F75" t="n">
         <v>2</v>
@@ -5106,13 +5106,13 @@
         <v>703.00545384</v>
       </c>
       <c r="Q75" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R75" t="n">
         <v>220.36</v>
       </c>
       <c r="S75" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T75" t="n">
         <v>3000</v>
@@ -5132,7 +5132,7 @@
         <v>1.22954208631452</v>
       </c>
       <c r="E76" t="n">
-        <v>75.94672192951562</v>
+        <v>75.91212623102716</v>
       </c>
       <c r="F76" t="n">
         <v>2</v>
@@ -5168,13 +5168,13 @@
         <v>703.00545384</v>
       </c>
       <c r="Q76" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R76" t="n">
         <v>546.08</v>
       </c>
       <c r="S76" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T76" t="n">
         <v>3000</v>
@@ -5194,7 +5194,7 @@
         <v>1.570661462759655</v>
       </c>
       <c r="E77" t="n">
-        <v>62.76095687058967</v>
+        <v>62.7399095501229</v>
       </c>
       <c r="F77" t="n">
         <v>2</v>
@@ -5230,13 +5230,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q77" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R77" t="n">
         <v>220.36</v>
       </c>
       <c r="S77" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T77" t="n">
         <v>3000</v>
@@ -5256,7 +5256,7 @@
         <v>3.287455501299847</v>
       </c>
       <c r="E78" t="n">
-        <v>82.91058636084767</v>
+        <v>82.88953904038092</v>
       </c>
       <c r="F78" t="n">
         <v>2</v>
@@ -5292,13 +5292,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q78" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R78" t="n">
         <v>220.36</v>
       </c>
       <c r="S78" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T78" t="n">
         <v>3000</v>
@@ -5318,7 +5318,7 @@
         <v>3.818068609863658</v>
       </c>
       <c r="E79" t="n">
-        <v>13.35908923013189</v>
+        <v>13.33022599579605</v>
       </c>
       <c r="F79" t="n">
         <v>2</v>
@@ -5354,13 +5354,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q79" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R79" t="n">
         <v>546.08</v>
       </c>
       <c r="S79" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T79" t="n">
         <v>3000</v>
@@ -5380,7 +5380,7 @@
         <v>5.345296053809121</v>
       </c>
       <c r="E80" t="n">
-        <v>13.35908923013189</v>
+        <v>13.33022599579605</v>
       </c>
       <c r="F80" t="n">
         <v>2</v>
@@ -5416,13 +5416,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q80" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R80" t="n">
         <v>546.08</v>
       </c>
       <c r="S80" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T80" t="n">
         <v>3000</v>
@@ -5442,7 +5442,7 @@
         <v>1.095818500433282</v>
       </c>
       <c r="E81" t="n">
-        <v>82.91058636084767</v>
+        <v>82.88953904038092</v>
       </c>
       <c r="F81" t="n">
         <v>2</v>
@@ -5478,13 +5478,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q81" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R81" t="n">
         <v>220.36</v>
       </c>
       <c r="S81" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T81" t="n">
         <v>3000</v>
@@ -5504,7 +5504,7 @@
         <v>2.391486505666307</v>
       </c>
       <c r="E82" t="n">
-        <v>3.308375310494415</v>
+        <v>3.285214091541177</v>
       </c>
       <c r="F82" t="n">
         <v>2</v>
@@ -5540,13 +5540,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q82" t="n">
-        <v>3505.72</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="R82" t="n">
         <v>1326.1</v>
       </c>
       <c r="S82" t="n">
-        <v>1165.66</v>
+        <v>26.18</v>
       </c>
       <c r="T82" t="n">
         <v>3000</v>
@@ -5566,7 +5566,7 @@
         <v>1.527227443945463</v>
       </c>
       <c r="E83" t="n">
-        <v>13.35908923013189</v>
+        <v>13.33022599579605</v>
       </c>
       <c r="F83" t="n">
         <v>2</v>
@@ -5602,13 +5602,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q83" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R83" t="n">
         <v>546.08</v>
       </c>
       <c r="S83" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T83" t="n">
         <v>3000</v>
@@ -5628,7 +5628,7 @@
         <v>4.711984388278966</v>
       </c>
       <c r="E84" t="n">
-        <v>62.76095687058967</v>
+        <v>62.7399095501229</v>
       </c>
       <c r="F84" t="n">
         <v>2</v>
@@ -5664,13 +5664,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q84" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R84" t="n">
         <v>220.36</v>
       </c>
       <c r="S84" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T84" t="n">
         <v>3000</v>
@@ -5690,7 +5690,7 @@
         <v>3.141322925519311</v>
       </c>
       <c r="E85" t="n">
-        <v>62.76095687058967</v>
+        <v>62.7399095501229</v>
       </c>
       <c r="F85" t="n">
         <v>2</v>
@@ -5726,13 +5726,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q85" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R85" t="n">
         <v>220.36</v>
       </c>
       <c r="S85" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T85" t="n">
         <v>3000</v>
@@ -5752,7 +5752,7 @@
         <v>1.619426228628243</v>
       </c>
       <c r="E86" t="n">
-        <v>298.2330148341655</v>
+        <v>298.2119675136988</v>
       </c>
       <c r="F86" t="n">
         <v>2</v>
@@ -5788,13 +5788,13 @@
         <v>703.00545384</v>
       </c>
       <c r="Q86" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R86" t="n">
         <v>220.36</v>
       </c>
       <c r="S86" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T86" t="n">
         <v>3000</v>
@@ -5814,7 +5814,7 @@
         <v>2.290841165918195</v>
       </c>
       <c r="E87" t="n">
-        <v>13.35908923013189</v>
+        <v>13.33022599579605</v>
       </c>
       <c r="F87" t="n">
         <v>2</v>
@@ -5850,13 +5850,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q87" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R87" t="n">
         <v>546.08</v>
       </c>
       <c r="S87" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T87" t="n">
         <v>3000</v>
@@ -5876,7 +5876,7 @@
         <v>10.99463023931759</v>
       </c>
       <c r="E88" t="n">
-        <v>62.76095687058967</v>
+        <v>62.7399095501229</v>
       </c>
       <c r="F88" t="n">
         <v>2</v>
@@ -5912,13 +5912,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q88" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R88" t="n">
         <v>220.36</v>
       </c>
       <c r="S88" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T88" t="n">
         <v>3000</v>
@@ -5938,7 +5938,7 @@
         <v>6.242079715670261</v>
       </c>
       <c r="E89" t="n">
-        <v>5.777523602080223</v>
+        <v>5.751940322103896</v>
       </c>
       <c r="F89" t="n">
         <v>2</v>
@@ -5974,13 +5974,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q89" t="n">
-        <v>2116.29</v>
+        <v>42.39</v>
       </c>
       <c r="R89" t="n">
         <v>914.66</v>
       </c>
       <c r="S89" t="n">
-        <v>801.585</v>
+        <v>19.65</v>
       </c>
       <c r="T89" t="n">
         <v>3000</v>
@@ -6000,7 +6000,7 @@
         <v>1.224297720630019</v>
       </c>
       <c r="E90" t="n">
-        <v>13.2275063309872</v>
+        <v>13.19864309665136</v>
       </c>
       <c r="F90" t="n">
         <v>2</v>
@@ -6036,13 +6036,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q90" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R90" t="n">
         <v>546.08</v>
       </c>
       <c r="S90" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T90" t="n">
         <v>3000</v>
@@ -6062,7 +6062,7 @@
         <v>3.171494831411509</v>
       </c>
       <c r="E91" t="n">
-        <v>17.63793698200517</v>
+        <v>17.60907374766933</v>
       </c>
       <c r="F91" t="n">
         <v>2</v>
@@ -6098,13 +6098,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q91" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R91" t="n">
         <v>546.08</v>
       </c>
       <c r="S91" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T91" t="n">
         <v>3000</v>
@@ -6124,7 +6124,7 @@
         <v>2.193320940567687</v>
       </c>
       <c r="E92" t="n">
-        <v>3.25336631452332</v>
+        <v>3.230365038035811</v>
       </c>
       <c r="F92" t="n">
         <v>2</v>
@@ -6160,13 +6160,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q92" t="n">
-        <v>3505.72</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="R92" t="n">
         <v>1326.1</v>
       </c>
       <c r="S92" t="n">
-        <v>1165.66</v>
+        <v>26.18</v>
       </c>
       <c r="T92" t="n">
         <v>3000</v>
@@ -6186,7 +6186,7 @@
         <v>2.040269259649053</v>
       </c>
       <c r="E93" t="n">
-        <v>5.83483166290713</v>
+        <v>5.809248382930803</v>
       </c>
       <c r="F93" t="n">
         <v>2</v>
@@ -6222,13 +6222,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q93" t="n">
-        <v>2116.29</v>
+        <v>42.39</v>
       </c>
       <c r="R93" t="n">
         <v>914.66</v>
       </c>
       <c r="S93" t="n">
-        <v>801.585</v>
+        <v>19.65</v>
       </c>
       <c r="T93" t="n">
         <v>3000</v>
@@ -6248,7 +6248,7 @@
         <v>7.670729503032977</v>
       </c>
       <c r="E94" t="n">
-        <v>82.91058636084767</v>
+        <v>82.88953904038092</v>
       </c>
       <c r="F94" t="n">
         <v>2</v>
@@ -6284,13 +6284,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q94" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R94" t="n">
         <v>220.36</v>
       </c>
       <c r="S94" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T94" t="n">
         <v>3000</v>
@@ -6310,7 +6310,7 @@
         <v>1.856513018878587</v>
       </c>
       <c r="E95" t="n">
-        <v>62.14131653310422</v>
+        <v>62.12026921263746</v>
       </c>
       <c r="F95" t="n">
         <v>2</v>
@@ -6346,13 +6346,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q95" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R95" t="n">
         <v>220.36</v>
       </c>
       <c r="S95" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T95" t="n">
         <v>3000</v>
@@ -6372,7 +6372,7 @@
         <v>1.774130615064986</v>
       </c>
       <c r="E96" t="n">
-        <v>7.82231299292982</v>
+        <v>7.796317893720655</v>
       </c>
       <c r="F96" t="n">
         <v>2</v>
@@ -6408,13 +6408,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q96" t="n">
-        <v>2116.29</v>
+        <v>42.39</v>
       </c>
       <c r="R96" t="n">
         <v>914.66</v>
       </c>
       <c r="S96" t="n">
-        <v>801.585</v>
+        <v>19.65</v>
       </c>
       <c r="T96" t="n">
         <v>3000</v>
@@ -6434,7 +6434,7 @@
         <v>5.569539056635763</v>
       </c>
       <c r="E97" t="n">
-        <v>62.14131653310422</v>
+        <v>62.12026921263746</v>
       </c>
       <c r="F97" t="n">
         <v>2</v>
@@ -6470,13 +6470,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q97" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R97" t="n">
         <v>220.36</v>
       </c>
       <c r="S97" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T97" t="n">
         <v>3000</v>
@@ -6496,7 +6496,7 @@
         <v>2.448595441260037</v>
       </c>
       <c r="E98" t="n">
-        <v>13.2275063309872</v>
+        <v>13.19864309665136</v>
       </c>
       <c r="F98" t="n">
         <v>2</v>
@@ -6532,13 +6532,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q98" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R98" t="n">
         <v>546.08</v>
       </c>
       <c r="S98" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T98" t="n">
         <v>3000</v>
@@ -6558,7 +6558,7 @@
         <v>16.70861716990729</v>
       </c>
       <c r="E99" t="n">
-        <v>62.14131653310422</v>
+        <v>62.12026921263746</v>
       </c>
       <c r="F99" t="n">
         <v>2</v>
@@ -6594,13 +6594,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q99" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R99" t="n">
         <v>220.36</v>
       </c>
       <c r="S99" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T99" t="n">
         <v>3000</v>
@@ -6620,7 +6620,7 @@
         <v>2.080693238556754</v>
       </c>
       <c r="E100" t="n">
-        <v>5.777523602080223</v>
+        <v>5.751940322103896</v>
       </c>
       <c r="F100" t="n">
         <v>2</v>
@@ -6656,13 +6656,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q100" t="n">
-        <v>2116.29</v>
+        <v>42.39</v>
       </c>
       <c r="R100" t="n">
         <v>914.66</v>
       </c>
       <c r="S100" t="n">
-        <v>801.585</v>
+        <v>19.65</v>
       </c>
       <c r="T100" t="n">
         <v>3000</v>
@@ -6682,7 +6682,7 @@
         <v>2.856376963508674</v>
       </c>
       <c r="E101" t="n">
-        <v>5.83483166290713</v>
+        <v>5.809248382930803</v>
       </c>
       <c r="F101" t="n">
         <v>2</v>
@@ -6718,13 +6718,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q101" t="n">
-        <v>2116.29</v>
+        <v>42.39</v>
       </c>
       <c r="R101" t="n">
         <v>914.66</v>
       </c>
       <c r="S101" t="n">
-        <v>801.585</v>
+        <v>19.65</v>
       </c>
       <c r="T101" t="n">
         <v>3000</v>
@@ -6744,7 +6744,7 @@
         <v>5.479092502166411</v>
       </c>
       <c r="E102" t="n">
-        <v>82.91058636084767</v>
+        <v>82.88953904038092</v>
       </c>
       <c r="F102" t="n">
         <v>2</v>
@@ -6780,13 +6780,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q102" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R102" t="n">
         <v>220.36</v>
       </c>
       <c r="S102" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T102" t="n">
         <v>3000</v>
@@ -6806,7 +6806,7 @@
         <v>11.01867948567017</v>
       </c>
       <c r="E103" t="n">
-        <v>13.2275063309872</v>
+        <v>13.19864309665136</v>
       </c>
       <c r="F103" t="n">
         <v>2</v>
@@ -6842,13 +6842,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q103" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R103" t="n">
         <v>546.08</v>
       </c>
       <c r="S103" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T103" t="n">
         <v>3000</v>
@@ -6868,7 +6868,7 @@
         <v>3.070649316794762</v>
       </c>
       <c r="E104" t="n">
-        <v>3.25336631452332</v>
+        <v>3.230365038035811</v>
       </c>
       <c r="F104" t="n">
         <v>2</v>
@@ -6904,13 +6904,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q104" t="n">
-        <v>3505.72</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="R104" t="n">
         <v>1326.1</v>
       </c>
       <c r="S104" t="n">
-        <v>1165.66</v>
+        <v>26.18</v>
       </c>
       <c r="T104" t="n">
         <v>3000</v>
@@ -6930,7 +6930,7 @@
         <v>2.265353451008221</v>
       </c>
       <c r="E105" t="n">
-        <v>17.63793698200517</v>
+        <v>17.60907374766933</v>
       </c>
       <c r="F105" t="n">
         <v>2</v>
@@ -6966,13 +6966,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q105" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R105" t="n">
         <v>546.08</v>
       </c>
       <c r="S105" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T105" t="n">
         <v>3000</v>
@@ -6992,7 +6992,7 @@
         <v>3.672893161890055</v>
       </c>
       <c r="E106" t="n">
-        <v>13.2275063309872</v>
+        <v>13.19864309665136</v>
       </c>
       <c r="F106" t="n">
         <v>2</v>
@@ -7028,13 +7028,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q106" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R106" t="n">
         <v>546.08</v>
       </c>
       <c r="S106" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T106" t="n">
         <v>3000</v>
@@ -7054,7 +7054,7 @@
         <v>3.713026037757175</v>
       </c>
       <c r="E107" t="n">
-        <v>62.14131653310422</v>
+        <v>62.12026921263746</v>
       </c>
       <c r="F107" t="n">
         <v>2</v>
@@ -7090,13 +7090,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q107" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R107" t="n">
         <v>220.36</v>
       </c>
       <c r="S107" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T107" t="n">
         <v>3000</v>
@@ -7116,7 +7116,7 @@
         <v>1.359212070604933</v>
       </c>
       <c r="E108" t="n">
-        <v>6.728547443461539</v>
+        <v>6.699684209125701</v>
       </c>
       <c r="F108" t="n">
         <v>4</v>
@@ -7152,13 +7152,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q108" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R108" t="n">
         <v>1092.16</v>
       </c>
       <c r="S108" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T108" t="n">
         <v>3000</v>
@@ -7178,7 +7178,7 @@
         <v>8.57008404441013</v>
       </c>
       <c r="E109" t="n">
-        <v>6.773359008885369</v>
+        <v>6.74449577454953</v>
       </c>
       <c r="F109" t="n">
         <v>4</v>
@@ -7214,13 +7214,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q109" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R109" t="n">
         <v>1092.16</v>
       </c>
       <c r="S109" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T109" t="n">
         <v>3000</v>
@@ -7240,7 +7240,7 @@
         <v>12.99559113215011</v>
       </c>
       <c r="E110" t="n">
-        <v>31.74792916404962</v>
+        <v>31.72688184358286</v>
       </c>
       <c r="F110" t="n">
         <v>4</v>
@@ -7276,13 +7276,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q110" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R110" t="n">
         <v>440.72</v>
       </c>
       <c r="S110" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T110" t="n">
         <v>3000</v>
@@ -7302,7 +7302,7 @@
         <v>2.281025076512125</v>
       </c>
       <c r="E111" t="n">
-        <v>2.994483014937363</v>
+        <v>2.968487915728197</v>
       </c>
       <c r="F111" t="n">
         <v>4</v>
@@ -7338,13 +7338,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q111" t="n">
-        <v>4232.58</v>
+        <v>84.78</v>
       </c>
       <c r="R111" t="n">
         <v>1829.32</v>
       </c>
       <c r="S111" t="n">
-        <v>1603.17</v>
+        <v>39.3</v>
       </c>
       <c r="T111" t="n">
         <v>3000</v>
@@ -7364,7 +7364,7 @@
         <v>9.862366503899541</v>
       </c>
       <c r="E112" t="n">
-        <v>31.53690589504611</v>
+        <v>31.51585857457935</v>
       </c>
       <c r="F112" t="n">
         <v>4</v>
@@ -7400,13 +7400,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q112" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R112" t="n">
         <v>440.72</v>
       </c>
       <c r="S112" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T112" t="n">
         <v>3000</v>
@@ -7426,7 +7426,7 @@
         <v>9.282565094392938</v>
       </c>
       <c r="E113" t="n">
-        <v>31.74792916404962</v>
+        <v>31.72688184358286</v>
       </c>
       <c r="F113" t="n">
         <v>4</v>
@@ -7462,13 +7462,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q113" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R113" t="n">
         <v>440.72</v>
       </c>
       <c r="S113" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T113" t="n">
         <v>3000</v>
@@ -7488,7 +7488,7 @@
         <v>4.077636211814798</v>
       </c>
       <c r="E114" t="n">
-        <v>6.728547443461539</v>
+        <v>6.699684209125701</v>
       </c>
       <c r="F114" t="n">
         <v>4</v>
@@ -7524,13 +7524,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q114" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R114" t="n">
         <v>1092.16</v>
       </c>
       <c r="S114" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T114" t="n">
         <v>3000</v>
@@ -7550,7 +7550,7 @@
         <v>6.121488603150093</v>
       </c>
       <c r="E115" t="n">
-        <v>6.773359008885369</v>
+        <v>6.74449577454953</v>
       </c>
       <c r="F115" t="n">
         <v>4</v>
@@ -7586,13 +7586,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q115" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R115" t="n">
         <v>1092.16</v>
       </c>
       <c r="S115" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T115" t="n">
         <v>3000</v>
@@ -7612,7 +7612,7 @@
         <v>14.1359531648369</v>
       </c>
       <c r="E116" t="n">
-        <v>31.30020373848205</v>
+        <v>31.27915641801529</v>
       </c>
       <c r="F116" t="n">
         <v>4</v>
@@ -7648,13 +7648,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q116" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R116" t="n">
         <v>440.72</v>
       </c>
       <c r="S116" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T116" t="n">
         <v>3000</v>
@@ -7674,7 +7674,7 @@
         <v>6.872523497754584</v>
       </c>
       <c r="E117" t="n">
-        <v>6.678282872047589</v>
+        <v>6.64941963771175</v>
       </c>
       <c r="F117" t="n">
         <v>4</v>
@@ -7710,13 +7710,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q117" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R117" t="n">
         <v>1092.16</v>
       </c>
       <c r="S117" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T117" t="n">
         <v>3000</v>
@@ -7736,7 +7736,7 @@
         <v>1.580839825261526</v>
       </c>
       <c r="E118" t="n">
-        <v>24.40355953791425</v>
+        <v>24.36896383942579</v>
       </c>
       <c r="F118" t="n">
         <v>4</v>
@@ -7772,13 +7772,13 @@
         <v>1406.01090768</v>
       </c>
       <c r="Q118" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R118" t="n">
         <v>1092.16</v>
       </c>
       <c r="S118" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T118" t="n">
         <v>3000</v>
@@ -7798,7 +7798,7 @@
         <v>2.914967211530838</v>
       </c>
       <c r="E119" t="n">
-        <v>95.72874554831728</v>
+        <v>95.70769822785053</v>
       </c>
       <c r="F119" t="n">
         <v>4</v>
@@ -7834,13 +7834,13 @@
         <v>1406.01090768</v>
       </c>
       <c r="Q119" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R119" t="n">
         <v>440.72</v>
       </c>
       <c r="S119" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T119" t="n">
         <v>3000</v>
@@ -7860,7 +7860,7 @@
         <v>7.853307313798277</v>
       </c>
       <c r="E120" t="n">
-        <v>31.30020373848205</v>
+        <v>31.27915641801529</v>
       </c>
       <c r="F120" t="n">
         <v>4</v>
@@ -7896,13 +7896,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q120" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R120" t="n">
         <v>440.72</v>
       </c>
       <c r="S120" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T120" t="n">
         <v>3000</v>
@@ -7922,7 +7922,7 @@
         <v>2.191637000866565</v>
       </c>
       <c r="E121" t="n">
-        <v>31.53690589504611</v>
+        <v>31.51585857457935</v>
       </c>
       <c r="F121" t="n">
         <v>4</v>
@@ -7958,13 +7958,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q121" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R121" t="n">
         <v>440.72</v>
       </c>
       <c r="S121" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T121" t="n">
         <v>3000</v>
@@ -7984,7 +7984,7 @@
         <v>2.267196720079541</v>
       </c>
       <c r="E122" t="n">
-        <v>95.72874554831728</v>
+        <v>95.70769822785053</v>
       </c>
       <c r="F122" t="n">
         <v>4</v>
@@ -8020,13 +8020,13 @@
         <v>1406.01090768</v>
       </c>
       <c r="Q122" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R122" t="n">
         <v>440.72</v>
       </c>
       <c r="S122" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T122" t="n">
         <v>3000</v>
@@ -8046,7 +8046,7 @@
         <v>0.6477704914512973</v>
       </c>
       <c r="E123" t="n">
-        <v>95.72874554831728</v>
+        <v>95.70769822785053</v>
       </c>
       <c r="F123" t="n">
         <v>4</v>
@@ -8082,13 +8082,13 @@
         <v>1406.01090768</v>
       </c>
       <c r="Q123" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R123" t="n">
         <v>440.72</v>
       </c>
       <c r="S123" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T123" t="n">
         <v>3000</v>
@@ -8108,7 +8108,7 @@
         <v>0.9716557371769459</v>
       </c>
       <c r="E124" t="n">
-        <v>95.72874554831728</v>
+        <v>95.70769822785053</v>
       </c>
       <c r="F124" t="n">
         <v>4</v>
@@ -8144,13 +8144,13 @@
         <v>1406.01090768</v>
       </c>
       <c r="Q124" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R124" t="n">
         <v>440.72</v>
       </c>
       <c r="S124" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T124" t="n">
         <v>3000</v>
@@ -8170,7 +8170,7 @@
         <v>1.22954208631452</v>
       </c>
       <c r="E125" t="n">
-        <v>24.40355953791425</v>
+        <v>24.36896383942579</v>
       </c>
       <c r="F125" t="n">
         <v>4</v>
@@ -8206,13 +8206,13 @@
         <v>1406.01090768</v>
       </c>
       <c r="Q125" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R125" t="n">
         <v>1092.16</v>
       </c>
       <c r="S125" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T125" t="n">
         <v>3000</v>
@@ -8232,7 +8232,7 @@
         <v>1.570661462759655</v>
       </c>
       <c r="E126" t="n">
-        <v>31.30020373848205</v>
+        <v>31.27915641801529</v>
       </c>
       <c r="F126" t="n">
         <v>4</v>
@@ -8268,13 +8268,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q126" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R126" t="n">
         <v>440.72</v>
       </c>
       <c r="S126" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T126" t="n">
         <v>3000</v>
@@ -8294,7 +8294,7 @@
         <v>3.287455501299847</v>
       </c>
       <c r="E127" t="n">
-        <v>31.53690589504611</v>
+        <v>31.51585857457935</v>
       </c>
       <c r="F127" t="n">
         <v>4</v>
@@ -8330,13 +8330,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q127" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R127" t="n">
         <v>440.72</v>
       </c>
       <c r="S127" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T127" t="n">
         <v>3000</v>
@@ -8356,7 +8356,7 @@
         <v>3.818068609863658</v>
       </c>
       <c r="E128" t="n">
-        <v>6.678282872047589</v>
+        <v>6.64941963771175</v>
       </c>
       <c r="F128" t="n">
         <v>4</v>
@@ -8392,13 +8392,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q128" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R128" t="n">
         <v>1092.16</v>
       </c>
       <c r="S128" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T128" t="n">
         <v>3000</v>
@@ -8418,7 +8418,7 @@
         <v>5.345296053809121</v>
       </c>
       <c r="E129" t="n">
-        <v>6.678282872047589</v>
+        <v>6.64941963771175</v>
       </c>
       <c r="F129" t="n">
         <v>4</v>
@@ -8454,13 +8454,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q129" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R129" t="n">
         <v>1092.16</v>
       </c>
       <c r="S129" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T129" t="n">
         <v>3000</v>
@@ -8480,7 +8480,7 @@
         <v>1.095818500433282</v>
       </c>
       <c r="E130" t="n">
-        <v>31.53690589504611</v>
+        <v>31.51585857457935</v>
       </c>
       <c r="F130" t="n">
         <v>4</v>
@@ -8516,13 +8516,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q130" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R130" t="n">
         <v>440.72</v>
       </c>
       <c r="S130" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T130" t="n">
         <v>3000</v>
@@ -8542,7 +8542,7 @@
         <v>1.527227443945463</v>
       </c>
       <c r="E131" t="n">
-        <v>6.678282872047589</v>
+        <v>6.64941963771175</v>
       </c>
       <c r="F131" t="n">
         <v>4</v>
@@ -8578,13 +8578,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q131" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R131" t="n">
         <v>1092.16</v>
       </c>
       <c r="S131" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T131" t="n">
         <v>3000</v>
@@ -8604,7 +8604,7 @@
         <v>4.711984388278966</v>
       </c>
       <c r="E132" t="n">
-        <v>31.30020373848205</v>
+        <v>31.27915641801529</v>
       </c>
       <c r="F132" t="n">
         <v>4</v>
@@ -8640,13 +8640,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q132" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R132" t="n">
         <v>440.72</v>
       </c>
       <c r="S132" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T132" t="n">
         <v>3000</v>
@@ -8666,7 +8666,7 @@
         <v>3.141322925519311</v>
       </c>
       <c r="E133" t="n">
-        <v>31.30020373848205</v>
+        <v>31.27915641801529</v>
       </c>
       <c r="F133" t="n">
         <v>4</v>
@@ -8702,13 +8702,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q133" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R133" t="n">
         <v>440.72</v>
       </c>
       <c r="S133" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T133" t="n">
         <v>3000</v>
@@ -8728,7 +8728,7 @@
         <v>1.619426228628243</v>
       </c>
       <c r="E134" t="n">
-        <v>95.72874554831728</v>
+        <v>95.70769822785053</v>
       </c>
       <c r="F134" t="n">
         <v>4</v>
@@ -8764,13 +8764,13 @@
         <v>1406.01090768</v>
       </c>
       <c r="Q134" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R134" t="n">
         <v>440.72</v>
       </c>
       <c r="S134" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T134" t="n">
         <v>3000</v>
@@ -8790,7 +8790,7 @@
         <v>2.290841165918195</v>
       </c>
       <c r="E135" t="n">
-        <v>6.678282872047589</v>
+        <v>6.64941963771175</v>
       </c>
       <c r="F135" t="n">
         <v>4</v>
@@ -8826,13 +8826,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q135" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R135" t="n">
         <v>1092.16</v>
       </c>
       <c r="S135" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T135" t="n">
         <v>3000</v>
@@ -8852,7 +8852,7 @@
         <v>10.99463023931759</v>
       </c>
       <c r="E136" t="n">
-        <v>31.30020373848205</v>
+        <v>31.27915641801529</v>
       </c>
       <c r="F136" t="n">
         <v>4</v>
@@ -8888,13 +8888,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q136" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R136" t="n">
         <v>440.72</v>
       </c>
       <c r="S136" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T136" t="n">
         <v>3000</v>
@@ -8914,7 +8914,7 @@
         <v>1.224297720630019</v>
       </c>
       <c r="E137" t="n">
-        <v>6.773359008885369</v>
+        <v>6.74449577454953</v>
       </c>
       <c r="F137" t="n">
         <v>4</v>
@@ -8950,13 +8950,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q137" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R137" t="n">
         <v>1092.16</v>
       </c>
       <c r="S137" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T137" t="n">
         <v>3000</v>
@@ -8976,7 +8976,7 @@
         <v>3.171494831411509</v>
       </c>
       <c r="E138" t="n">
-        <v>6.728547443461539</v>
+        <v>6.699684209125701</v>
       </c>
       <c r="F138" t="n">
         <v>4</v>
@@ -9012,13 +9012,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q138" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R138" t="n">
         <v>1092.16</v>
       </c>
       <c r="S138" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T138" t="n">
         <v>3000</v>
@@ -9038,7 +9038,7 @@
         <v>2.040269259649053</v>
       </c>
       <c r="E139" t="n">
-        <v>2.925152216485539</v>
+        <v>2.899568936509212</v>
       </c>
       <c r="F139" t="n">
         <v>4</v>
@@ -9074,13 +9074,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q139" t="n">
-        <v>4232.58</v>
+        <v>84.78</v>
       </c>
       <c r="R139" t="n">
         <v>1829.32</v>
       </c>
       <c r="S139" t="n">
-        <v>1603.17</v>
+        <v>39.3</v>
       </c>
       <c r="T139" t="n">
         <v>3000</v>
@@ -9100,7 +9100,7 @@
         <v>7.670729503032977</v>
       </c>
       <c r="E140" t="n">
-        <v>31.53690589504611</v>
+        <v>31.51585857457935</v>
       </c>
       <c r="F140" t="n">
         <v>4</v>
@@ -9136,13 +9136,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q140" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R140" t="n">
         <v>440.72</v>
       </c>
       <c r="S140" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T140" t="n">
         <v>3000</v>
@@ -9162,7 +9162,7 @@
         <v>1.856513018878587</v>
       </c>
       <c r="E141" t="n">
-        <v>31.74792916404962</v>
+        <v>31.72688184358286</v>
       </c>
       <c r="F141" t="n">
         <v>4</v>
@@ -9198,13 +9198,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q141" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R141" t="n">
         <v>440.72</v>
       </c>
       <c r="S141" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T141" t="n">
         <v>3000</v>
@@ -9224,7 +9224,7 @@
         <v>1.774130615064986</v>
       </c>
       <c r="E142" t="n">
-        <v>2.994483014937363</v>
+        <v>2.968487915728197</v>
       </c>
       <c r="F142" t="n">
         <v>4</v>
@@ -9260,13 +9260,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q142" t="n">
-        <v>4232.58</v>
+        <v>84.78</v>
       </c>
       <c r="R142" t="n">
         <v>1829.32</v>
       </c>
       <c r="S142" t="n">
-        <v>1603.17</v>
+        <v>39.3</v>
       </c>
       <c r="T142" t="n">
         <v>3000</v>
@@ -9286,7 +9286,7 @@
         <v>5.569539056635763</v>
       </c>
       <c r="E143" t="n">
-        <v>31.74792916404962</v>
+        <v>31.72688184358286</v>
       </c>
       <c r="F143" t="n">
         <v>4</v>
@@ -9322,13 +9322,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q143" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R143" t="n">
         <v>440.72</v>
       </c>
       <c r="S143" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T143" t="n">
         <v>3000</v>
@@ -9348,7 +9348,7 @@
         <v>2.448595441260037</v>
       </c>
       <c r="E144" t="n">
-        <v>6.773359008885369</v>
+        <v>6.74449577454953</v>
       </c>
       <c r="F144" t="n">
         <v>4</v>
@@ -9384,13 +9384,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q144" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R144" t="n">
         <v>1092.16</v>
       </c>
       <c r="S144" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T144" t="n">
         <v>3000</v>
@@ -9410,7 +9410,7 @@
         <v>16.70861716990729</v>
       </c>
       <c r="E145" t="n">
-        <v>31.74792916404962</v>
+        <v>31.72688184358286</v>
       </c>
       <c r="F145" t="n">
         <v>4</v>
@@ -9446,13 +9446,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q145" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R145" t="n">
         <v>440.72</v>
       </c>
       <c r="S145" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T145" t="n">
         <v>3000</v>
@@ -9472,7 +9472,7 @@
         <v>2.080693238556754</v>
       </c>
       <c r="E146" t="n">
-        <v>2.966560553499722</v>
+        <v>2.940977273523396</v>
       </c>
       <c r="F146" t="n">
         <v>4</v>
@@ -9508,13 +9508,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q146" t="n">
-        <v>4232.58</v>
+        <v>84.78</v>
       </c>
       <c r="R146" t="n">
         <v>1829.32</v>
       </c>
       <c r="S146" t="n">
-        <v>1603.17</v>
+        <v>39.3</v>
       </c>
       <c r="T146" t="n">
         <v>3000</v>
@@ -9534,7 +9534,7 @@
         <v>2.856376963508674</v>
       </c>
       <c r="E147" t="n">
-        <v>2.925152216485539</v>
+        <v>2.899568936509212</v>
       </c>
       <c r="F147" t="n">
         <v>4</v>
@@ -9570,13 +9570,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q147" t="n">
-        <v>4232.58</v>
+        <v>84.78</v>
       </c>
       <c r="R147" t="n">
         <v>1829.32</v>
       </c>
       <c r="S147" t="n">
-        <v>1603.17</v>
+        <v>39.3</v>
       </c>
       <c r="T147" t="n">
         <v>3000</v>
@@ -9596,7 +9596,7 @@
         <v>5.479092502166411</v>
       </c>
       <c r="E148" t="n">
-        <v>31.53690589504611</v>
+        <v>31.51585857457935</v>
       </c>
       <c r="F148" t="n">
         <v>4</v>
@@ -9632,13 +9632,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q148" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R148" t="n">
         <v>440.72</v>
       </c>
       <c r="S148" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T148" t="n">
         <v>3000</v>
@@ -9658,7 +9658,7 @@
         <v>11.01867948567017</v>
       </c>
       <c r="E149" t="n">
-        <v>6.773359008885369</v>
+        <v>6.74449577454953</v>
       </c>
       <c r="F149" t="n">
         <v>4</v>
@@ -9694,13 +9694,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q149" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R149" t="n">
         <v>1092.16</v>
       </c>
       <c r="S149" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T149" t="n">
         <v>3000</v>
@@ -9720,7 +9720,7 @@
         <v>2.265353451008221</v>
       </c>
       <c r="E150" t="n">
-        <v>6.728547443461539</v>
+        <v>6.699684209125701</v>
       </c>
       <c r="F150" t="n">
         <v>4</v>
@@ -9756,13 +9756,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q150" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R150" t="n">
         <v>1092.16</v>
       </c>
       <c r="S150" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T150" t="n">
         <v>3000</v>
@@ -9782,7 +9782,7 @@
         <v>3.672893161890055</v>
       </c>
       <c r="E151" t="n">
-        <v>6.773359008885369</v>
+        <v>6.74449577454953</v>
       </c>
       <c r="F151" t="n">
         <v>4</v>
@@ -9818,13 +9818,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q151" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R151" t="n">
         <v>1092.16</v>
       </c>
       <c r="S151" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T151" t="n">
         <v>3000</v>
@@ -9844,7 +9844,7 @@
         <v>3.713026037757175</v>
       </c>
       <c r="E152" t="n">
-        <v>31.74792916404962</v>
+        <v>31.72688184358286</v>
       </c>
       <c r="F152" t="n">
         <v>4</v>
@@ -9880,13 +9880,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q152" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R152" t="n">
         <v>440.72</v>
       </c>
       <c r="S152" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T152" t="n">
         <v>3000</v>
@@ -9906,7 +9906,7 @@
         <v>1.359212070604933</v>
       </c>
       <c r="E153" t="n">
-        <v>4.467376116033963</v>
+        <v>4.438512881698125</v>
       </c>
       <c r="F153" t="n">
         <v>6</v>
@@ -9942,13 +9942,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q153" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R153" t="n">
         <v>1638.24</v>
       </c>
       <c r="S153" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T153" t="n">
         <v>3000</v>
@@ -9968,7 +9968,7 @@
         <v>12.99559113215011</v>
       </c>
       <c r="E154" t="n">
-        <v>21.61768523318152</v>
+        <v>21.59663791271477</v>
       </c>
       <c r="F154" t="n">
         <v>6</v>
@@ -10004,13 +10004,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q154" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R154" t="n">
         <v>661.08</v>
       </c>
       <c r="S154" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T154" t="n">
         <v>3000</v>
@@ -10030,7 +10030,7 @@
         <v>9.862366503899541</v>
       </c>
       <c r="E155" t="n">
-        <v>20.88876716617601</v>
+        <v>20.86771984570925</v>
       </c>
       <c r="F155" t="n">
         <v>6</v>
@@ -10066,13 +10066,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q155" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R155" t="n">
         <v>661.08</v>
       </c>
       <c r="S155" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T155" t="n">
         <v>3000</v>
@@ -10092,7 +10092,7 @@
         <v>9.282565094392938</v>
       </c>
       <c r="E156" t="n">
-        <v>21.61768523318152</v>
+        <v>21.59663791271477</v>
       </c>
       <c r="F156" t="n">
         <v>6</v>
@@ -10128,13 +10128,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q156" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R156" t="n">
         <v>661.08</v>
       </c>
       <c r="S156" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T156" t="n">
         <v>3000</v>
@@ -10154,7 +10154,7 @@
         <v>4.077636211814798</v>
       </c>
       <c r="E157" t="n">
-        <v>4.467376116033963</v>
+        <v>4.438512881698125</v>
       </c>
       <c r="F157" t="n">
         <v>6</v>
@@ -10190,13 +10190,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q157" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R157" t="n">
         <v>1638.24</v>
       </c>
       <c r="S157" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T157" t="n">
         <v>3000</v>
@@ -10216,7 +10216,7 @@
         <v>6.121488603150093</v>
       </c>
       <c r="E158" t="n">
-        <v>4.62216454198563</v>
+        <v>4.593301307649792</v>
       </c>
       <c r="F158" t="n">
         <v>6</v>
@@ -10252,13 +10252,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q158" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R158" t="n">
         <v>1638.24</v>
       </c>
       <c r="S158" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T158" t="n">
         <v>3000</v>
@@ -10278,7 +10278,7 @@
         <v>14.1359531648369</v>
       </c>
       <c r="E159" t="n">
-        <v>21.16863420542943</v>
+        <v>21.14758688496268</v>
       </c>
       <c r="F159" t="n">
         <v>6</v>
@@ -10314,13 +10314,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q159" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R159" t="n">
         <v>661.08</v>
       </c>
       <c r="S159" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T159" t="n">
         <v>3000</v>
@@ -10340,7 +10340,7 @@
         <v>6.872523497754584</v>
       </c>
       <c r="E160" t="n">
-        <v>4.526806908660295</v>
+        <v>4.497943674324457</v>
       </c>
       <c r="F160" t="n">
         <v>6</v>
@@ -10376,13 +10376,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q160" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R160" t="n">
         <v>1638.24</v>
       </c>
       <c r="S160" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T160" t="n">
         <v>3000</v>
@@ -10402,7 +10402,7 @@
         <v>1.580839825261526</v>
       </c>
       <c r="E161" t="n">
-        <v>11.3193797443361</v>
+        <v>11.28478404584764</v>
       </c>
       <c r="F161" t="n">
         <v>6</v>
@@ -10438,13 +10438,13 @@
         <v>2109.01636152</v>
       </c>
       <c r="Q161" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R161" t="n">
         <v>1638.24</v>
       </c>
       <c r="S161" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T161" t="n">
         <v>3000</v>
@@ -10464,7 +10464,7 @@
         <v>2.914967211530838</v>
       </c>
       <c r="E162" t="n">
-        <v>44.32324100878711</v>
+        <v>44.30219368832036</v>
       </c>
       <c r="F162" t="n">
         <v>6</v>
@@ -10500,13 +10500,13 @@
         <v>2109.01636152</v>
       </c>
       <c r="Q162" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R162" t="n">
         <v>661.08</v>
       </c>
       <c r="S162" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T162" t="n">
         <v>3000</v>
@@ -10526,7 +10526,7 @@
         <v>7.853307313798277</v>
       </c>
       <c r="E163" t="n">
-        <v>21.16863420542943</v>
+        <v>21.14758688496268</v>
       </c>
       <c r="F163" t="n">
         <v>6</v>
@@ -10562,13 +10562,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q163" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R163" t="n">
         <v>661.08</v>
       </c>
       <c r="S163" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T163" t="n">
         <v>3000</v>
@@ -10588,7 +10588,7 @@
         <v>2.191637000866565</v>
       </c>
       <c r="E164" t="n">
-        <v>20.88876716617601</v>
+        <v>20.86771984570925</v>
       </c>
       <c r="F164" t="n">
         <v>6</v>
@@ -10624,13 +10624,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q164" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R164" t="n">
         <v>661.08</v>
       </c>
       <c r="S164" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T164" t="n">
         <v>3000</v>
@@ -10650,7 +10650,7 @@
         <v>2.267196720079541</v>
       </c>
       <c r="E165" t="n">
-        <v>44.32324100878711</v>
+        <v>44.30219368832036</v>
       </c>
       <c r="F165" t="n">
         <v>6</v>
@@ -10686,13 +10686,13 @@
         <v>2109.01636152</v>
       </c>
       <c r="Q165" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R165" t="n">
         <v>661.08</v>
       </c>
       <c r="S165" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T165" t="n">
         <v>3000</v>
@@ -10712,7 +10712,7 @@
         <v>0.6477704914512973</v>
       </c>
       <c r="E166" t="n">
-        <v>44.32324100878711</v>
+        <v>44.30219368832036</v>
       </c>
       <c r="F166" t="n">
         <v>6</v>
@@ -10748,13 +10748,13 @@
         <v>2109.01636152</v>
       </c>
       <c r="Q166" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R166" t="n">
         <v>661.08</v>
       </c>
       <c r="S166" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T166" t="n">
         <v>3000</v>
@@ -10774,7 +10774,7 @@
         <v>0.9716557371769459</v>
       </c>
       <c r="E167" t="n">
-        <v>44.32324100878711</v>
+        <v>44.30219368832036</v>
       </c>
       <c r="F167" t="n">
         <v>6</v>
@@ -10810,13 +10810,13 @@
         <v>2109.01636152</v>
       </c>
       <c r="Q167" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R167" t="n">
         <v>661.08</v>
       </c>
       <c r="S167" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T167" t="n">
         <v>3000</v>
@@ -10836,7 +10836,7 @@
         <v>1.22954208631452</v>
       </c>
       <c r="E168" t="n">
-        <v>11.3193797443361</v>
+        <v>11.28478404584764</v>
       </c>
       <c r="F168" t="n">
         <v>6</v>
@@ -10872,13 +10872,13 @@
         <v>2109.01636152</v>
       </c>
       <c r="Q168" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R168" t="n">
         <v>1638.24</v>
       </c>
       <c r="S168" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T168" t="n">
         <v>3000</v>
@@ -10898,7 +10898,7 @@
         <v>1.570661462759655</v>
       </c>
       <c r="E169" t="n">
-        <v>21.16863420542943</v>
+        <v>21.14758688496268</v>
       </c>
       <c r="F169" t="n">
         <v>6</v>
@@ -10934,13 +10934,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q169" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R169" t="n">
         <v>661.08</v>
       </c>
       <c r="S169" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T169" t="n">
         <v>3000</v>
@@ -10960,7 +10960,7 @@
         <v>3.287455501299847</v>
       </c>
       <c r="E170" t="n">
-        <v>20.88876716617601</v>
+        <v>20.86771984570925</v>
       </c>
       <c r="F170" t="n">
         <v>6</v>
@@ -10996,13 +10996,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q170" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R170" t="n">
         <v>661.08</v>
       </c>
       <c r="S170" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T170" t="n">
         <v>3000</v>
@@ -11022,7 +11022,7 @@
         <v>3.818068609863658</v>
       </c>
       <c r="E171" t="n">
-        <v>4.526806908660295</v>
+        <v>4.497943674324457</v>
       </c>
       <c r="F171" t="n">
         <v>6</v>
@@ -11058,13 +11058,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q171" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R171" t="n">
         <v>1638.24</v>
       </c>
       <c r="S171" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T171" t="n">
         <v>3000</v>
@@ -11084,7 +11084,7 @@
         <v>5.345296053809121</v>
       </c>
       <c r="E172" t="n">
-        <v>4.526806908660295</v>
+        <v>4.497943674324457</v>
       </c>
       <c r="F172" t="n">
         <v>6</v>
@@ -11120,13 +11120,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q172" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R172" t="n">
         <v>1638.24</v>
       </c>
       <c r="S172" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T172" t="n">
         <v>3000</v>
@@ -11146,7 +11146,7 @@
         <v>1.095818500433282</v>
       </c>
       <c r="E173" t="n">
-        <v>20.88876716617601</v>
+        <v>20.86771984570925</v>
       </c>
       <c r="F173" t="n">
         <v>6</v>
@@ -11182,13 +11182,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q173" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R173" t="n">
         <v>661.08</v>
       </c>
       <c r="S173" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T173" t="n">
         <v>3000</v>
@@ -11208,7 +11208,7 @@
         <v>1.527227443945463</v>
       </c>
       <c r="E174" t="n">
-        <v>4.526806908660295</v>
+        <v>4.497943674324457</v>
       </c>
       <c r="F174" t="n">
         <v>6</v>
@@ -11244,13 +11244,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q174" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R174" t="n">
         <v>1638.24</v>
       </c>
       <c r="S174" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T174" t="n">
         <v>3000</v>
@@ -11270,7 +11270,7 @@
         <v>4.711984388278966</v>
       </c>
       <c r="E175" t="n">
-        <v>21.16863420542943</v>
+        <v>21.14758688496268</v>
       </c>
       <c r="F175" t="n">
         <v>6</v>
@@ -11306,13 +11306,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q175" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R175" t="n">
         <v>661.08</v>
       </c>
       <c r="S175" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T175" t="n">
         <v>3000</v>
@@ -11332,7 +11332,7 @@
         <v>3.141322925519311</v>
       </c>
       <c r="E176" t="n">
-        <v>21.16863420542943</v>
+        <v>21.14758688496268</v>
       </c>
       <c r="F176" t="n">
         <v>6</v>
@@ -11368,13 +11368,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q176" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R176" t="n">
         <v>661.08</v>
       </c>
       <c r="S176" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T176" t="n">
         <v>3000</v>
@@ -11394,7 +11394,7 @@
         <v>1.619426228628243</v>
       </c>
       <c r="E177" t="n">
-        <v>44.32324100878711</v>
+        <v>44.30219368832036</v>
       </c>
       <c r="F177" t="n">
         <v>6</v>
@@ -11430,13 +11430,13 @@
         <v>2109.01636152</v>
       </c>
       <c r="Q177" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R177" t="n">
         <v>661.08</v>
       </c>
       <c r="S177" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T177" t="n">
         <v>3000</v>
@@ -11456,7 +11456,7 @@
         <v>2.290841165918195</v>
       </c>
       <c r="E178" t="n">
-        <v>4.526806908660295</v>
+        <v>4.497943674324457</v>
       </c>
       <c r="F178" t="n">
         <v>6</v>
@@ -11492,13 +11492,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q178" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R178" t="n">
         <v>1638.24</v>
       </c>
       <c r="S178" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T178" t="n">
         <v>3000</v>
@@ -11518,7 +11518,7 @@
         <v>10.99463023931759</v>
       </c>
       <c r="E179" t="n">
-        <v>21.16863420542943</v>
+        <v>21.14758688496268</v>
       </c>
       <c r="F179" t="n">
         <v>6</v>
@@ -11554,13 +11554,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q179" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R179" t="n">
         <v>661.08</v>
       </c>
       <c r="S179" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T179" t="n">
         <v>3000</v>
@@ -11580,7 +11580,7 @@
         <v>1.224297720630019</v>
       </c>
       <c r="E180" t="n">
-        <v>4.62216454198563</v>
+        <v>4.593301307649792</v>
       </c>
       <c r="F180" t="n">
         <v>6</v>
@@ -11616,13 +11616,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q180" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R180" t="n">
         <v>1638.24</v>
       </c>
       <c r="S180" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T180" t="n">
         <v>3000</v>
@@ -11642,7 +11642,7 @@
         <v>3.171494831411509</v>
       </c>
       <c r="E181" t="n">
-        <v>4.467376116033963</v>
+        <v>4.438512881698125</v>
       </c>
       <c r="F181" t="n">
         <v>6</v>
@@ -11678,13 +11678,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q181" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R181" t="n">
         <v>1638.24</v>
       </c>
       <c r="S181" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T181" t="n">
         <v>3000</v>
@@ -11704,7 +11704,7 @@
         <v>7.670729503032977</v>
       </c>
       <c r="E182" t="n">
-        <v>20.88876716617601</v>
+        <v>20.86771984570925</v>
       </c>
       <c r="F182" t="n">
         <v>6</v>
@@ -11740,13 +11740,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q182" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R182" t="n">
         <v>661.08</v>
       </c>
       <c r="S182" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T182" t="n">
         <v>3000</v>
@@ -11766,7 +11766,7 @@
         <v>1.856513018878587</v>
       </c>
       <c r="E183" t="n">
-        <v>21.61768523318152</v>
+        <v>21.59663791271477</v>
       </c>
       <c r="F183" t="n">
         <v>6</v>
@@ -11802,13 +11802,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q183" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R183" t="n">
         <v>661.08</v>
       </c>
       <c r="S183" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T183" t="n">
         <v>3000</v>
@@ -11828,7 +11828,7 @@
         <v>5.569539056635763</v>
       </c>
       <c r="E184" t="n">
-        <v>21.61768523318152</v>
+        <v>21.59663791271477</v>
       </c>
       <c r="F184" t="n">
         <v>6</v>
@@ -11864,13 +11864,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q184" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R184" t="n">
         <v>661.08</v>
       </c>
       <c r="S184" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T184" t="n">
         <v>3000</v>
@@ -11890,7 +11890,7 @@
         <v>2.448595441260037</v>
       </c>
       <c r="E185" t="n">
-        <v>4.62216454198563</v>
+        <v>4.593301307649792</v>
       </c>
       <c r="F185" t="n">
         <v>6</v>
@@ -11926,13 +11926,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q185" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R185" t="n">
         <v>1638.24</v>
       </c>
       <c r="S185" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T185" t="n">
         <v>3000</v>
@@ -11952,7 +11952,7 @@
         <v>16.70861716990729</v>
       </c>
       <c r="E186" t="n">
-        <v>21.61768523318152</v>
+        <v>21.59663791271477</v>
       </c>
       <c r="F186" t="n">
         <v>6</v>
@@ -11988,13 +11988,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q186" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R186" t="n">
         <v>661.08</v>
       </c>
       <c r="S186" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T186" t="n">
         <v>3000</v>
@@ -12014,7 +12014,7 @@
         <v>5.479092502166411</v>
       </c>
       <c r="E187" t="n">
-        <v>20.88876716617601</v>
+        <v>20.86771984570925</v>
       </c>
       <c r="F187" t="n">
         <v>6</v>
@@ -12050,13 +12050,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q187" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R187" t="n">
         <v>661.08</v>
       </c>
       <c r="S187" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T187" t="n">
         <v>3000</v>
@@ -12076,7 +12076,7 @@
         <v>2.265353451008221</v>
       </c>
       <c r="E188" t="n">
-        <v>4.467376116033963</v>
+        <v>4.438512881698125</v>
       </c>
       <c r="F188" t="n">
         <v>6</v>
@@ -12112,13 +12112,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q188" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R188" t="n">
         <v>1638.24</v>
       </c>
       <c r="S188" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T188" t="n">
         <v>3000</v>
@@ -12138,7 +12138,7 @@
         <v>3.672893161890055</v>
       </c>
       <c r="E189" t="n">
-        <v>4.62216454198563</v>
+        <v>4.593301307649792</v>
       </c>
       <c r="F189" t="n">
         <v>6</v>
@@ -12174,13 +12174,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q189" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R189" t="n">
         <v>1638.24</v>
       </c>
       <c r="S189" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T189" t="n">
         <v>3000</v>
@@ -12200,7 +12200,7 @@
         <v>3.713026037757175</v>
       </c>
       <c r="E190" t="n">
-        <v>21.61768523318152</v>
+        <v>21.59663791271477</v>
       </c>
       <c r="F190" t="n">
         <v>6</v>
@@ -12236,13 +12236,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q190" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R190" t="n">
         <v>661.08</v>
       </c>
       <c r="S190" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T190" t="n">
         <v>3000</v>
@@ -12262,7 +12262,7 @@
         <v>1.359212070604933</v>
       </c>
       <c r="E191" t="n">
-        <v>3.388144264419388</v>
+        <v>3.35928103008355</v>
       </c>
       <c r="F191" t="n">
         <v>8</v>
@@ -12298,13 +12298,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q191" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R191" t="n">
         <v>2184.32</v>
       </c>
       <c r="S191" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T191" t="n">
         <v>3000</v>
@@ -12324,7 +12324,7 @@
         <v>12.99559113215011</v>
       </c>
       <c r="E192" t="n">
-        <v>16.55256327182657</v>
+        <v>16.53151595135981</v>
       </c>
       <c r="F192" t="n">
         <v>8</v>
@@ -12360,13 +12360,13 @@
         <v>27950.93706399999</v>
       </c>
       <c r="Q192" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R192" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S192" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T192" t="n">
         <v>3000</v>
@@ -12386,7 +12386,7 @@
         <v>9.862366503899541</v>
       </c>
       <c r="E193" t="n">
-        <v>15.8065293289923</v>
+        <v>15.78548200852555</v>
       </c>
       <c r="F193" t="n">
         <v>8</v>
@@ -12422,13 +12422,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q193" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R193" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S193" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T193" t="n">
         <v>3000</v>
@@ -12448,7 +12448,7 @@
         <v>9.282565094392938</v>
       </c>
       <c r="E194" t="n">
-        <v>16.55256327182657</v>
+        <v>16.53151595135981</v>
       </c>
       <c r="F194" t="n">
         <v>8</v>
@@ -12484,13 +12484,13 @@
         <v>27950.93706399999</v>
       </c>
       <c r="Q194" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R194" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S194" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T194" t="n">
         <v>3000</v>
@@ -12510,7 +12510,7 @@
         <v>4.077636211814798</v>
       </c>
       <c r="E195" t="n">
-        <v>3.388144264419388</v>
+        <v>3.35928103008355</v>
       </c>
       <c r="F195" t="n">
         <v>8</v>
@@ -12546,13 +12546,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q195" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R195" t="n">
         <v>2184.32</v>
       </c>
       <c r="S195" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T195" t="n">
         <v>3000</v>
@@ -12572,7 +12572,7 @@
         <v>14.1359531648369</v>
       </c>
       <c r="E196" t="n">
-        <v>16.10351005395474</v>
+        <v>16.08246273348799</v>
       </c>
       <c r="F196" t="n">
         <v>8</v>
@@ -12608,13 +12608,13 @@
         <v>16304.811096</v>
       </c>
       <c r="Q196" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R196" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S196" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T196" t="n">
         <v>3000</v>
@@ -12634,7 +12634,7 @@
         <v>1.580839825261526</v>
       </c>
       <c r="E197" t="n">
-        <v>6.463599078349216</v>
+        <v>6.429003379860761</v>
       </c>
       <c r="F197" t="n">
         <v>8</v>
@@ -12670,13 +12670,13 @@
         <v>2812.02181536</v>
       </c>
       <c r="Q197" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R197" t="n">
         <v>2184.32</v>
       </c>
       <c r="S197" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T197" t="n">
         <v>3000</v>
@@ -12696,7 +12696,7 @@
         <v>2.914967211530838</v>
       </c>
       <c r="E198" t="n">
-        <v>25.24570928678613</v>
+        <v>25.22466196631937</v>
       </c>
       <c r="F198" t="n">
         <v>8</v>
@@ -12732,13 +12732,13 @@
         <v>2812.02181536</v>
       </c>
       <c r="Q198" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R198" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S198" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T198" t="n">
         <v>3000</v>
@@ -12758,7 +12758,7 @@
         <v>7.853307313798277</v>
       </c>
       <c r="E199" t="n">
-        <v>16.10351005395474</v>
+        <v>16.08246273348799</v>
       </c>
       <c r="F199" t="n">
         <v>8</v>
@@ -12794,13 +12794,13 @@
         <v>16304.811096</v>
       </c>
       <c r="Q199" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R199" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S199" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T199" t="n">
         <v>3000</v>
@@ -12820,7 +12820,7 @@
         <v>2.191637000866565</v>
       </c>
       <c r="E200" t="n">
-        <v>15.8065293289923</v>
+        <v>15.78548200852555</v>
       </c>
       <c r="F200" t="n">
         <v>8</v>
@@ -12856,13 +12856,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q200" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R200" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S200" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T200" t="n">
         <v>3000</v>
@@ -12882,7 +12882,7 @@
         <v>2.267196720079541</v>
       </c>
       <c r="E201" t="n">
-        <v>25.24570928678613</v>
+        <v>25.22466196631937</v>
       </c>
       <c r="F201" t="n">
         <v>8</v>
@@ -12918,13 +12918,13 @@
         <v>2812.02181536</v>
       </c>
       <c r="Q201" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R201" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S201" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T201" t="n">
         <v>3000</v>
@@ -12944,7 +12944,7 @@
         <v>0.6477704914512973</v>
       </c>
       <c r="E202" t="n">
-        <v>25.24570928678613</v>
+        <v>25.22466196631937</v>
       </c>
       <c r="F202" t="n">
         <v>8</v>
@@ -12980,13 +12980,13 @@
         <v>2812.02181536</v>
       </c>
       <c r="Q202" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R202" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S202" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T202" t="n">
         <v>3000</v>
@@ -13006,7 +13006,7 @@
         <v>0.9716557371769459</v>
       </c>
       <c r="E203" t="n">
-        <v>25.24570928678613</v>
+        <v>25.22466196631937</v>
       </c>
       <c r="F203" t="n">
         <v>8</v>
@@ -13042,13 +13042,13 @@
         <v>2812.02181536</v>
       </c>
       <c r="Q203" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R203" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S203" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T203" t="n">
         <v>3000</v>
@@ -13068,7 +13068,7 @@
         <v>1.22954208631452</v>
       </c>
       <c r="E204" t="n">
-        <v>6.463599078349216</v>
+        <v>6.429003379860761</v>
       </c>
       <c r="F204" t="n">
         <v>8</v>
@@ -13104,13 +13104,13 @@
         <v>2812.02181536</v>
       </c>
       <c r="Q204" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R204" t="n">
         <v>2184.32</v>
       </c>
       <c r="S204" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T204" t="n">
         <v>3000</v>
@@ -13130,7 +13130,7 @@
         <v>1.570661462759655</v>
       </c>
       <c r="E205" t="n">
-        <v>16.10351005395474</v>
+        <v>16.08246273348799</v>
       </c>
       <c r="F205" t="n">
         <v>8</v>
@@ -13166,13 +13166,13 @@
         <v>16304.811096</v>
       </c>
       <c r="Q205" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R205" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S205" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T205" t="n">
         <v>3000</v>
@@ -13192,7 +13192,7 @@
         <v>3.287455501299847</v>
       </c>
       <c r="E206" t="n">
-        <v>15.8065293289923</v>
+        <v>15.78548200852555</v>
       </c>
       <c r="F206" t="n">
         <v>8</v>
@@ -13228,13 +13228,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q206" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R206" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S206" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T206" t="n">
         <v>3000</v>
@@ -13254,7 +13254,7 @@
         <v>3.818068609863658</v>
       </c>
       <c r="E207" t="n">
-        <v>3.451209210996674</v>
+        <v>3.422345976660836</v>
       </c>
       <c r="F207" t="n">
         <v>8</v>
@@ -13290,13 +13290,13 @@
         <v>16304.811096</v>
       </c>
       <c r="Q207" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R207" t="n">
         <v>2184.32</v>
       </c>
       <c r="S207" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T207" t="n">
         <v>3000</v>
@@ -13316,7 +13316,7 @@
         <v>1.095818500433282</v>
       </c>
       <c r="E208" t="n">
-        <v>15.8065293289923</v>
+        <v>15.78548200852555</v>
       </c>
       <c r="F208" t="n">
         <v>8</v>
@@ -13352,13 +13352,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q208" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R208" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S208" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T208" t="n">
         <v>3000</v>
@@ -13378,7 +13378,7 @@
         <v>1.527227443945463</v>
       </c>
       <c r="E209" t="n">
-        <v>3.451209210996674</v>
+        <v>3.422345976660836</v>
       </c>
       <c r="F209" t="n">
         <v>8</v>
@@ -13414,13 +13414,13 @@
         <v>16304.811096</v>
       </c>
       <c r="Q209" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R209" t="n">
         <v>2184.32</v>
       </c>
       <c r="S209" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T209" t="n">
         <v>3000</v>
@@ -13440,7 +13440,7 @@
         <v>4.711984388278966</v>
       </c>
       <c r="E210" t="n">
-        <v>16.10351005395474</v>
+        <v>16.08246273348799</v>
       </c>
       <c r="F210" t="n">
         <v>8</v>
@@ -13476,13 +13476,13 @@
         <v>16304.811096</v>
       </c>
       <c r="Q210" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R210" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S210" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T210" t="n">
         <v>3000</v>
@@ -13502,7 +13502,7 @@
         <v>3.141322925519311</v>
       </c>
       <c r="E211" t="n">
-        <v>16.10351005395474</v>
+        <v>16.08246273348799</v>
       </c>
       <c r="F211" t="n">
         <v>8</v>
@@ -13538,13 +13538,13 @@
         <v>16304.811096</v>
       </c>
       <c r="Q211" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R211" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S211" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T211" t="n">
         <v>3000</v>
@@ -13564,7 +13564,7 @@
         <v>1.619426228628243</v>
       </c>
       <c r="E212" t="n">
-        <v>25.24570928678613</v>
+        <v>25.22466196631937</v>
       </c>
       <c r="F212" t="n">
         <v>8</v>
@@ -13600,13 +13600,13 @@
         <v>2812.02181536</v>
       </c>
       <c r="Q212" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R212" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S212" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T212" t="n">
         <v>3000</v>
@@ -13626,7 +13626,7 @@
         <v>2.290841165918195</v>
       </c>
       <c r="E213" t="n">
-        <v>3.451209210996674</v>
+        <v>3.422345976660836</v>
       </c>
       <c r="F213" t="n">
         <v>8</v>
@@ -13662,13 +13662,13 @@
         <v>16304.811096</v>
       </c>
       <c r="Q213" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R213" t="n">
         <v>2184.32</v>
       </c>
       <c r="S213" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T213" t="n">
         <v>3000</v>
@@ -13688,7 +13688,7 @@
         <v>10.99463023931759</v>
       </c>
       <c r="E214" t="n">
-        <v>16.10351005395474</v>
+        <v>16.08246273348799</v>
       </c>
       <c r="F214" t="n">
         <v>8</v>
@@ -13724,13 +13724,13 @@
         <v>16304.811096</v>
       </c>
       <c r="Q214" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R214" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S214" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T214" t="n">
         <v>3000</v>
@@ -13750,7 +13750,7 @@
         <v>1.224297720630019</v>
       </c>
       <c r="E215" t="n">
-        <v>3.546567309401973</v>
+        <v>3.517704075066135</v>
       </c>
       <c r="F215" t="n">
         <v>8</v>
@@ -13786,13 +13786,13 @@
         <v>27950.93706399999</v>
       </c>
       <c r="Q215" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R215" t="n">
         <v>2184.32</v>
       </c>
       <c r="S215" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T215" t="n">
         <v>3000</v>
@@ -13812,7 +13812,7 @@
         <v>3.171494831411509</v>
       </c>
       <c r="E216" t="n">
-        <v>3.388144264419388</v>
+        <v>3.35928103008355</v>
       </c>
       <c r="F216" t="n">
         <v>8</v>
@@ -13848,13 +13848,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q216" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R216" t="n">
         <v>2184.32</v>
       </c>
       <c r="S216" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T216" t="n">
         <v>3000</v>
@@ -13874,7 +13874,7 @@
         <v>7.670729503032977</v>
       </c>
       <c r="E217" t="n">
-        <v>15.8065293289923</v>
+        <v>15.78548200852555</v>
       </c>
       <c r="F217" t="n">
         <v>8</v>
@@ -13910,13 +13910,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q217" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R217" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S217" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T217" t="n">
         <v>3000</v>
@@ -13936,7 +13936,7 @@
         <v>1.856513018878587</v>
       </c>
       <c r="E218" t="n">
-        <v>16.55256327182657</v>
+        <v>16.53151595135981</v>
       </c>
       <c r="F218" t="n">
         <v>8</v>
@@ -13972,13 +13972,13 @@
         <v>27950.93706399999</v>
       </c>
       <c r="Q218" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R218" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S218" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T218" t="n">
         <v>3000</v>
@@ -13998,7 +13998,7 @@
         <v>5.569539056635763</v>
       </c>
       <c r="E219" t="n">
-        <v>16.55256327182657</v>
+        <v>16.53151595135981</v>
       </c>
       <c r="F219" t="n">
         <v>8</v>
@@ -14034,13 +14034,13 @@
         <v>27950.93706399999</v>
       </c>
       <c r="Q219" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R219" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S219" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T219" t="n">
         <v>3000</v>
@@ -14060,7 +14060,7 @@
         <v>2.448595441260037</v>
       </c>
       <c r="E220" t="n">
-        <v>3.546567309401973</v>
+        <v>3.517704075066135</v>
       </c>
       <c r="F220" t="n">
         <v>8</v>
@@ -14096,13 +14096,13 @@
         <v>27950.93706399999</v>
       </c>
       <c r="Q220" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R220" t="n">
         <v>2184.32</v>
       </c>
       <c r="S220" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T220" t="n">
         <v>3000</v>
@@ -14122,7 +14122,7 @@
         <v>16.70861716990729</v>
       </c>
       <c r="E221" t="n">
-        <v>16.55256327182657</v>
+        <v>16.53151595135981</v>
       </c>
       <c r="F221" t="n">
         <v>8</v>
@@ -14158,13 +14158,13 @@
         <v>27950.93706399999</v>
       </c>
       <c r="Q221" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R221" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S221" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T221" t="n">
         <v>3000</v>
@@ -14184,7 +14184,7 @@
         <v>5.479092502166411</v>
       </c>
       <c r="E222" t="n">
-        <v>15.8065293289923</v>
+        <v>15.78548200852555</v>
       </c>
       <c r="F222" t="n">
         <v>8</v>
@@ -14220,13 +14220,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q222" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R222" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S222" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T222" t="n">
         <v>3000</v>
@@ -14246,7 +14246,7 @@
         <v>2.265353451008221</v>
       </c>
       <c r="E223" t="n">
-        <v>3.388144264419388</v>
+        <v>3.35928103008355</v>
       </c>
       <c r="F223" t="n">
         <v>8</v>
@@ -14282,13 +14282,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q223" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R223" t="n">
         <v>2184.32</v>
       </c>
       <c r="S223" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T223" t="n">
         <v>3000</v>
@@ -14308,7 +14308,7 @@
         <v>3.672893161890055</v>
       </c>
       <c r="E224" t="n">
-        <v>3.546567309401973</v>
+        <v>3.517704075066135</v>
       </c>
       <c r="F224" t="n">
         <v>8</v>
@@ -14344,13 +14344,13 @@
         <v>27950.93706399999</v>
       </c>
       <c r="Q224" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R224" t="n">
         <v>2184.32</v>
       </c>
       <c r="S224" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T224" t="n">
         <v>3000</v>
@@ -14370,7 +14370,7 @@
         <v>3.713026037757175</v>
       </c>
       <c r="E225" t="n">
-        <v>16.55256327182657</v>
+        <v>16.53151595135981</v>
       </c>
       <c r="F225" t="n">
         <v>8</v>
@@ -14406,13 +14406,13 @@
         <v>27950.93706399999</v>
       </c>
       <c r="Q225" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R225" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S225" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T225" t="n">
         <v>3000</v>
@@ -14432,7 +14432,7 @@
         <v>1.359212070604933</v>
       </c>
       <c r="E226" t="n">
-        <v>2.742650558053792</v>
+        <v>2.713787323717954</v>
       </c>
       <c r="F226" t="n">
         <v>10</v>
@@ -14468,13 +14468,13 @@
         <v>11451.26633</v>
       </c>
       <c r="Q226" t="n">
-        <v>5034.300000000001</v>
+        <v>100.9</v>
       </c>
       <c r="R226" t="n">
         <v>2730.4</v>
       </c>
       <c r="S226" t="n">
-        <v>2148.5</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="T226" t="n">
         <v>3000</v>
@@ -14494,7 +14494,7 @@
         <v>12.99559113215011</v>
       </c>
       <c r="E227" t="n">
-        <v>13.51349009501362</v>
+        <v>13.49244277454687</v>
       </c>
       <c r="F227" t="n">
         <v>10</v>
@@ -14530,13 +14530,13 @@
         <v>34938.67132999999</v>
       </c>
       <c r="Q227" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R227" t="n">
         <v>1101.8</v>
       </c>
       <c r="S227" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T227" t="n">
         <v>3000</v>
@@ -14556,7 +14556,7 @@
         <v>9.862366503899541</v>
       </c>
       <c r="E228" t="n">
-        <v>12.7668186929067</v>
+        <v>12.74577137243994</v>
       </c>
       <c r="F228" t="n">
         <v>10</v>
@@ -14592,13 +14592,13 @@
         <v>11451.26633</v>
       </c>
       <c r="Q228" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R228" t="n">
         <v>1101.8</v>
       </c>
       <c r="S228" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T228" t="n">
         <v>3000</v>
@@ -14618,7 +14618,7 @@
         <v>9.282565094392938</v>
       </c>
       <c r="E229" t="n">
-        <v>13.51349009501362</v>
+        <v>13.49244277454687</v>
       </c>
       <c r="F229" t="n">
         <v>10</v>
@@ -14654,13 +14654,13 @@
         <v>34938.67132999999</v>
       </c>
       <c r="Q229" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R229" t="n">
         <v>1101.8</v>
       </c>
       <c r="S229" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T229" t="n">
         <v>3000</v>
@@ -14680,7 +14680,7 @@
         <v>14.1359531648369</v>
       </c>
       <c r="E230" t="n">
-        <v>13.06443687307073</v>
+        <v>13.04338955260397</v>
       </c>
       <c r="F230" t="n">
         <v>10</v>
@@ -14716,13 +14716,13 @@
         <v>20381.01387</v>
       </c>
       <c r="Q230" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R230" t="n">
         <v>1101.8</v>
       </c>
       <c r="S230" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T230" t="n">
         <v>3000</v>
@@ -14742,7 +14742,7 @@
         <v>1.580839825261526</v>
       </c>
       <c r="E231" t="n">
-        <v>4.290503581090693</v>
+        <v>4.255907882602238</v>
       </c>
       <c r="F231" t="n">
         <v>10</v>
@@ -14778,13 +14778,13 @@
         <v>3515.0272692</v>
       </c>
       <c r="Q231" t="n">
-        <v>5034.300000000001</v>
+        <v>100.9</v>
       </c>
       <c r="R231" t="n">
         <v>2730.4</v>
       </c>
       <c r="S231" t="n">
-        <v>2148.5</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="T231" t="n">
         <v>3000</v>
@@ -14804,7 +14804,7 @@
         <v>2.914967211530838</v>
       </c>
       <c r="E232" t="n">
-        <v>16.70798875622727</v>
+        <v>16.68694143576051</v>
       </c>
       <c r="F232" t="n">
         <v>10</v>
@@ -14840,13 +14840,13 @@
         <v>3515.0272692</v>
       </c>
       <c r="Q232" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R232" t="n">
         <v>1101.8</v>
       </c>
       <c r="S232" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T232" t="n">
         <v>3000</v>
@@ -14866,7 +14866,7 @@
         <v>7.853307313798277</v>
       </c>
       <c r="E233" t="n">
-        <v>13.06443687307073</v>
+        <v>13.04338955260397</v>
       </c>
       <c r="F233" t="n">
         <v>10</v>
@@ -14902,13 +14902,13 @@
         <v>20381.01387</v>
       </c>
       <c r="Q233" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R233" t="n">
         <v>1101.8</v>
       </c>
       <c r="S233" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T233" t="n">
         <v>3000</v>
@@ -14928,7 +14928,7 @@
         <v>2.191637000866565</v>
       </c>
       <c r="E234" t="n">
-        <v>12.7668186929067</v>
+        <v>12.74577137243994</v>
       </c>
       <c r="F234" t="n">
         <v>10</v>
@@ -14964,13 +14964,13 @@
         <v>11451.26633</v>
       </c>
       <c r="Q234" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R234" t="n">
         <v>1101.8</v>
       </c>
       <c r="S234" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T234" t="n">
         <v>3000</v>
@@ -14990,7 +14990,7 @@
         <v>2.267196720079541</v>
       </c>
       <c r="E235" t="n">
-        <v>16.70798875622727</v>
+        <v>16.68694143576051</v>
       </c>
       <c r="F235" t="n">
         <v>10</v>
@@ -15026,13 +15026,13 @@
         <v>3515.0272692</v>
       </c>
       <c r="Q235" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R235" t="n">
         <v>1101.8</v>
       </c>
       <c r="S235" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T235" t="n">
         <v>3000</v>
@@ -15052,7 +15052,7 @@
         <v>0.6477704914512973</v>
       </c>
       <c r="E236" t="n">
-        <v>16.70798875622727</v>
+        <v>16.68694143576051</v>
       </c>
       <c r="F236" t="n">
         <v>10</v>
@@ -15088,13 +15088,13 @@
         <v>3515.0272692</v>
       </c>
       <c r="Q236" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R236" t="n">
         <v>1101.8</v>
       </c>
       <c r="S236" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T236" t="n">
         <v>3000</v>
@@ -15114,7 +15114,7 @@
         <v>0.9716557371769459</v>
       </c>
       <c r="E237" t="n">
-        <v>16.70798875622727</v>
+        <v>16.68694143576051</v>
       </c>
       <c r="F237" t="n">
         <v>10</v>
@@ -15150,13 +15150,13 @@
         <v>3515.0272692</v>
       </c>
       <c r="Q237" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R237" t="n">
         <v>1101.8</v>
       </c>
       <c r="S237" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T237" t="n">
         <v>3000</v>
@@ -15176,7 +15176,7 @@
         <v>1.22954208631452</v>
       </c>
       <c r="E238" t="n">
-        <v>4.290503581090693</v>
+        <v>4.255907882602238</v>
       </c>
       <c r="F238" t="n">
         <v>10</v>
@@ -15212,13 +15212,13 @@
         <v>3515.0272692</v>
       </c>
       <c r="Q238" t="n">
-        <v>5034.300000000001</v>
+        <v>100.9</v>
       </c>
       <c r="R238" t="n">
         <v>2730.4</v>
       </c>
       <c r="S238" t="n">
-        <v>2148.5</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="T238" t="n">
         <v>3000</v>
@@ -15238,7 +15238,7 @@
         <v>1.570661462759655</v>
       </c>
       <c r="E239" t="n">
-        <v>13.06443687307073</v>
+        <v>13.04338955260397</v>
       </c>
       <c r="F239" t="n">
         <v>10</v>
@@ -15274,13 +15274,13 @@
         <v>20381.01387</v>
       </c>
       <c r="Q239" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R239" t="n">
         <v>1101.8</v>
       </c>
       <c r="S239" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T239" t="n">
         <v>3000</v>
@@ -15300,7 +15300,7 @@
         <v>3.287455501299847</v>
       </c>
       <c r="E240" t="n">
-        <v>12.7668186929067</v>
+        <v>12.74577137243994</v>
       </c>
       <c r="F240" t="n">
         <v>10</v>
@@ -15336,13 +15336,13 @@
         <v>11451.26633</v>
       </c>
       <c r="Q240" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R240" t="n">
         <v>1101.8</v>
       </c>
       <c r="S240" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T240" t="n">
         <v>3000</v>
@@ -15362,7 +15362,7 @@
         <v>1.095818500433282</v>
       </c>
       <c r="E241" t="n">
-        <v>12.7668186929067</v>
+        <v>12.74577137243994</v>
       </c>
       <c r="F241" t="n">
         <v>10</v>
@@ -15398,13 +15398,13 @@
         <v>11451.26633</v>
       </c>
       <c r="Q241" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R241" t="n">
         <v>1101.8</v>
       </c>
       <c r="S241" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T241" t="n">
         <v>3000</v>
@@ -15424,7 +15424,7 @@
         <v>1.527227443945463</v>
       </c>
       <c r="E242" t="n">
-        <v>2.805850870581979</v>
+        <v>2.776987636246142</v>
       </c>
       <c r="F242" t="n">
         <v>10</v>
@@ -15460,13 +15460,13 @@
         <v>20381.01387</v>
       </c>
       <c r="Q242" t="n">
-        <v>5034.300000000001</v>
+        <v>100.9</v>
       </c>
       <c r="R242" t="n">
         <v>2730.4</v>
       </c>
       <c r="S242" t="n">
-        <v>2148.5</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="T242" t="n">
         <v>3000</v>
@@ -15486,7 +15486,7 @@
         <v>4.711984388278966</v>
       </c>
       <c r="E243" t="n">
-        <v>13.06443687307073</v>
+        <v>13.04338955260397</v>
       </c>
       <c r="F243" t="n">
         <v>10</v>
@@ -15522,13 +15522,13 @@
         <v>20381.01387</v>
       </c>
       <c r="Q243" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R243" t="n">
         <v>1101.8</v>
       </c>
       <c r="S243" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T243" t="n">
         <v>3000</v>
@@ -15548,7 +15548,7 @@
         <v>3.141322925519311</v>
       </c>
       <c r="E244" t="n">
-        <v>13.06443687307073</v>
+        <v>13.04338955260397</v>
       </c>
       <c r="F244" t="n">
         <v>10</v>
@@ -15584,13 +15584,13 @@
         <v>20381.01387</v>
       </c>
       <c r="Q244" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R244" t="n">
         <v>1101.8</v>
       </c>
       <c r="S244" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T244" t="n">
         <v>3000</v>
@@ -15610,7 +15610,7 @@
         <v>1.619426228628243</v>
       </c>
       <c r="E245" t="n">
-        <v>16.70798875622727</v>
+        <v>16.68694143576051</v>
       </c>
       <c r="F245" t="n">
         <v>10</v>
@@ -15646,13 +15646,13 @@
         <v>3515.0272692</v>
       </c>
       <c r="Q245" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R245" t="n">
         <v>1101.8</v>
       </c>
       <c r="S245" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T245" t="n">
         <v>3000</v>
@@ -15672,7 +15672,7 @@
         <v>2.290841165918195</v>
       </c>
       <c r="E246" t="n">
-        <v>2.805850870581979</v>
+        <v>2.776987636246142</v>
       </c>
       <c r="F246" t="n">
         <v>10</v>
@@ -15708,13 +15708,13 @@
         <v>20381.01387</v>
       </c>
       <c r="Q246" t="n">
-        <v>5034.300000000001</v>
+        <v>100.9</v>
       </c>
       <c r="R246" t="n">
         <v>2730.4</v>
       </c>
       <c r="S246" t="n">
-        <v>2148.5</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="T246" t="n">
         <v>3000</v>
@@ -15734,7 +15734,7 @@
         <v>10.99463023931759</v>
       </c>
       <c r="E247" t="n">
-        <v>13.06443687307073</v>
+        <v>13.04338955260397</v>
       </c>
       <c r="F247" t="n">
         <v>10</v>
@@ -15770,13 +15770,13 @@
         <v>20381.01387</v>
       </c>
       <c r="Q247" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R247" t="n">
         <v>1101.8</v>
       </c>
       <c r="S247" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T247" t="n">
         <v>3000</v>
@@ -15796,7 +15796,7 @@
         <v>1.224297720630019</v>
       </c>
       <c r="E248" t="n">
-        <v>2.901208969851784</v>
+        <v>2.872345735515946</v>
       </c>
       <c r="F248" t="n">
         <v>10</v>
@@ -15832,13 +15832,13 @@
         <v>34938.67132999999</v>
       </c>
       <c r="Q248" t="n">
-        <v>5034.300000000001</v>
+        <v>100.9</v>
       </c>
       <c r="R248" t="n">
         <v>2730.4</v>
       </c>
       <c r="S248" t="n">
-        <v>2148.5</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="T248" t="n">
         <v>3000</v>
@@ -15858,7 +15858,7 @@
         <v>7.670729503032977</v>
       </c>
       <c r="E249" t="n">
-        <v>12.7668186929067</v>
+        <v>12.74577137243994</v>
       </c>
       <c r="F249" t="n">
         <v>10</v>
@@ -15894,13 +15894,13 @@
         <v>11451.26633</v>
       </c>
       <c r="Q249" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R249" t="n">
         <v>1101.8</v>
       </c>
       <c r="S249" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T249" t="n">
         <v>3000</v>
@@ -15920,7 +15920,7 @@
         <v>1.856513018878587</v>
       </c>
       <c r="E250" t="n">
-        <v>13.51349009501362</v>
+        <v>13.49244277454687</v>
       </c>
       <c r="F250" t="n">
         <v>10</v>
@@ -15956,13 +15956,13 @@
         <v>34938.67132999999</v>
       </c>
       <c r="Q250" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R250" t="n">
         <v>1101.8</v>
       </c>
       <c r="S250" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T250" t="n">
         <v>3000</v>
@@ -15982,7 +15982,7 @@
         <v>5.569539056635763</v>
       </c>
       <c r="E251" t="n">
-        <v>13.51349009501362</v>
+        <v>13.49244277454687</v>
       </c>
       <c r="F251" t="n">
         <v>10</v>
@@ -16018,13 +16018,13 @@
         <v>34938.67132999999</v>
       </c>
       <c r="Q251" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R251" t="n">
         <v>1101.8</v>
       </c>
       <c r="S251" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T251" t="n">
         <v>3000</v>
@@ -16044,7 +16044,7 @@
         <v>16.70861716990729</v>
       </c>
       <c r="E252" t="n">
-        <v>13.51349009501362</v>
+        <v>13.49244277454687</v>
       </c>
       <c r="F252" t="n">
         <v>10</v>
@@ -16080,13 +16080,13 @@
         <v>34938.67132999999</v>
       </c>
       <c r="Q252" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R252" t="n">
         <v>1101.8</v>
       </c>
       <c r="S252" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T252" t="n">
         <v>3000</v>
@@ -16106,7 +16106,7 @@
         <v>5.479092502166411</v>
       </c>
       <c r="E253" t="n">
-        <v>12.7668186929067</v>
+        <v>12.74577137243994</v>
       </c>
       <c r="F253" t="n">
         <v>10</v>
@@ -16142,13 +16142,13 @@
         <v>11451.26633</v>
       </c>
       <c r="Q253" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R253" t="n">
         <v>1101.8</v>
       </c>
       <c r="S253" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T253" t="n">
         <v>3000</v>
@@ -16168,7 +16168,7 @@
         <v>2.265353451008221</v>
       </c>
       <c r="E254" t="n">
-        <v>2.742650558053792</v>
+        <v>2.713787323717954</v>
       </c>
       <c r="F254" t="n">
         <v>10</v>
@@ -16204,13 +16204,13 @@
         <v>11451.26633</v>
       </c>
       <c r="Q254" t="n">
-        <v>5034.300000000001</v>
+        <v>100.9</v>
       </c>
       <c r="R254" t="n">
         <v>2730.4</v>
       </c>
       <c r="S254" t="n">
-        <v>2148.5</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="T254" t="n">
         <v>3000</v>
@@ -16230,7 +16230,7 @@
         <v>3.713026037757175</v>
       </c>
       <c r="E255" t="n">
-        <v>13.51349009501362</v>
+        <v>13.49244277454687</v>
       </c>
       <c r="F255" t="n">
         <v>10</v>
@@ -16266,13 +16266,13 @@
         <v>34938.67132999999</v>
       </c>
       <c r="Q255" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R255" t="n">
         <v>1101.8</v>
       </c>
       <c r="S255" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T255" t="n">
         <v>3000</v>
@@ -16292,7 +16292,7 @@
         <v>12.99559113215011</v>
       </c>
       <c r="E256" t="n">
-        <v>11.48744131047166</v>
+        <v>11.4663939900049</v>
       </c>
       <c r="F256" t="n">
         <v>12</v>
@@ -16328,13 +16328,13 @@
         <v>41926.40559599999</v>
       </c>
       <c r="Q256" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R256" t="n">
         <v>1322.16</v>
       </c>
       <c r="S256" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T256" t="n">
         <v>3000</v>
@@ -16354,7 +16354,7 @@
         <v>9.862366503899541</v>
       </c>
       <c r="E257" t="n">
-        <v>10.740744562466</v>
+        <v>10.71969724199924</v>
       </c>
       <c r="F257" t="n">
         <v>12</v>
@@ -16390,13 +16390,13 @@
         <v>13741.519596</v>
       </c>
       <c r="Q257" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R257" t="n">
         <v>1322.16</v>
       </c>
       <c r="S257" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T257" t="n">
         <v>3000</v>
@@ -16416,7 +16416,7 @@
         <v>9.282565094392938</v>
       </c>
       <c r="E258" t="n">
-        <v>11.48744131047166</v>
+        <v>11.4663939900049</v>
       </c>
       <c r="F258" t="n">
         <v>12</v>
@@ -16452,13 +16452,13 @@
         <v>41926.40559599999</v>
       </c>
       <c r="Q258" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R258" t="n">
         <v>1322.16</v>
       </c>
       <c r="S258" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T258" t="n">
         <v>3000</v>
@@ -16478,7 +16478,7 @@
         <v>14.1359531648369</v>
       </c>
       <c r="E259" t="n">
-        <v>11.03838808852069</v>
+        <v>11.01734076805394</v>
       </c>
       <c r="F259" t="n">
         <v>12</v>
@@ -16514,13 +16514,13 @@
         <v>24457.216644</v>
       </c>
       <c r="Q259" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R259" t="n">
         <v>1322.16</v>
       </c>
       <c r="S259" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T259" t="n">
         <v>3000</v>
@@ -16540,7 +16540,7 @@
         <v>2.914967211530838</v>
       </c>
       <c r="E260" t="n">
-        <v>12.34649379027359</v>
+        <v>12.32544646980683</v>
       </c>
       <c r="F260" t="n">
         <v>12</v>
@@ -16576,13 +16576,13 @@
         <v>4218.03272304</v>
       </c>
       <c r="Q260" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R260" t="n">
         <v>1322.16</v>
       </c>
       <c r="S260" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T260" t="n">
         <v>3000</v>
@@ -16602,7 +16602,7 @@
         <v>7.853307313798277</v>
       </c>
       <c r="E261" t="n">
-        <v>11.03838808852069</v>
+        <v>11.01734076805394</v>
       </c>
       <c r="F261" t="n">
         <v>12</v>
@@ -16638,13 +16638,13 @@
         <v>24457.216644</v>
       </c>
       <c r="Q261" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R261" t="n">
         <v>1322.16</v>
       </c>
       <c r="S261" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T261" t="n">
         <v>3000</v>
@@ -16664,7 +16664,7 @@
         <v>2.191637000866565</v>
       </c>
       <c r="E262" t="n">
-        <v>10.740744562466</v>
+        <v>10.71969724199924</v>
       </c>
       <c r="F262" t="n">
         <v>12</v>
@@ -16700,13 +16700,13 @@
         <v>13741.519596</v>
       </c>
       <c r="Q262" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R262" t="n">
         <v>1322.16</v>
       </c>
       <c r="S262" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T262" t="n">
         <v>3000</v>
@@ -16726,7 +16726,7 @@
         <v>2.267196720079541</v>
       </c>
       <c r="E263" t="n">
-        <v>12.34649379027359</v>
+        <v>12.32544646980683</v>
       </c>
       <c r="F263" t="n">
         <v>12</v>
@@ -16762,13 +16762,13 @@
         <v>4218.03272304</v>
       </c>
       <c r="Q263" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R263" t="n">
         <v>1322.16</v>
       </c>
       <c r="S263" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T263" t="n">
         <v>3000</v>
@@ -16788,7 +16788,7 @@
         <v>0.6477704914512973</v>
       </c>
       <c r="E264" t="n">
-        <v>12.34649379027359</v>
+        <v>12.32544646980683</v>
       </c>
       <c r="F264" t="n">
         <v>12</v>
@@ -16824,13 +16824,13 @@
         <v>4218.03272304</v>
       </c>
       <c r="Q264" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R264" t="n">
         <v>1322.16</v>
       </c>
       <c r="S264" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T264" t="n">
         <v>3000</v>
@@ -16850,7 +16850,7 @@
         <v>0.9716557371769459</v>
       </c>
       <c r="E265" t="n">
-        <v>12.34649379027359</v>
+        <v>12.32544646980683</v>
       </c>
       <c r="F265" t="n">
         <v>12</v>
@@ -16886,13 +16886,13 @@
         <v>4218.03272304</v>
       </c>
       <c r="Q265" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R265" t="n">
         <v>1322.16</v>
       </c>
       <c r="S265" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T265" t="n">
         <v>3000</v>
@@ -16912,7 +16912,7 @@
         <v>1.570661462759655</v>
       </c>
       <c r="E266" t="n">
-        <v>11.03838808852069</v>
+        <v>11.01734076805394</v>
       </c>
       <c r="F266" t="n">
         <v>12</v>
@@ -16948,13 +16948,13 @@
         <v>24457.216644</v>
       </c>
       <c r="Q266" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R266" t="n">
         <v>1322.16</v>
       </c>
       <c r="S266" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T266" t="n">
         <v>3000</v>
@@ -16974,7 +16974,7 @@
         <v>3.287455501299847</v>
       </c>
       <c r="E267" t="n">
-        <v>10.740744562466</v>
+        <v>10.71969724199924</v>
       </c>
       <c r="F267" t="n">
         <v>12</v>
@@ -17010,13 +17010,13 @@
         <v>13741.519596</v>
       </c>
       <c r="Q267" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R267" t="n">
         <v>1322.16</v>
       </c>
       <c r="S267" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T267" t="n">
         <v>3000</v>
@@ -17036,7 +17036,7 @@
         <v>1.095818500433282</v>
       </c>
       <c r="E268" t="n">
-        <v>10.740744562466</v>
+        <v>10.71969724199924</v>
       </c>
       <c r="F268" t="n">
         <v>12</v>
@@ -17072,13 +17072,13 @@
         <v>13741.519596</v>
       </c>
       <c r="Q268" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R268" t="n">
         <v>1322.16</v>
       </c>
       <c r="S268" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T268" t="n">
         <v>3000</v>
@@ -17098,7 +17098,7 @@
         <v>4.711984388278966</v>
       </c>
       <c r="E269" t="n">
-        <v>11.03838808852069</v>
+        <v>11.01734076805394</v>
       </c>
       <c r="F269" t="n">
         <v>12</v>
@@ -17134,13 +17134,13 @@
         <v>24457.216644</v>
       </c>
       <c r="Q269" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R269" t="n">
         <v>1322.16</v>
       </c>
       <c r="S269" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T269" t="n">
         <v>3000</v>
@@ -17160,7 +17160,7 @@
         <v>3.141322925519311</v>
       </c>
       <c r="E270" t="n">
-        <v>11.03838808852069</v>
+        <v>11.01734076805394</v>
       </c>
       <c r="F270" t="n">
         <v>12</v>
@@ -17196,13 +17196,13 @@
         <v>24457.216644</v>
       </c>
       <c r="Q270" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R270" t="n">
         <v>1322.16</v>
       </c>
       <c r="S270" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T270" t="n">
         <v>3000</v>
@@ -17222,7 +17222,7 @@
         <v>1.619426228628243</v>
       </c>
       <c r="E271" t="n">
-        <v>12.34649379027359</v>
+        <v>12.32544646980683</v>
       </c>
       <c r="F271" t="n">
         <v>12</v>
@@ -17258,13 +17258,13 @@
         <v>4218.03272304</v>
       </c>
       <c r="Q271" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R271" t="n">
         <v>1322.16</v>
       </c>
       <c r="S271" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T271" t="n">
         <v>3000</v>
@@ -17284,7 +17284,7 @@
         <v>10.99463023931759</v>
       </c>
       <c r="E272" t="n">
-        <v>11.03838808852069</v>
+        <v>11.01734076805394</v>
       </c>
       <c r="F272" t="n">
         <v>12</v>
@@ -17320,13 +17320,13 @@
         <v>24457.216644</v>
       </c>
       <c r="Q272" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R272" t="n">
         <v>1322.16</v>
       </c>
       <c r="S272" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T272" t="n">
         <v>3000</v>
@@ -17346,7 +17346,7 @@
         <v>7.670729503032977</v>
       </c>
       <c r="E273" t="n">
-        <v>10.740744562466</v>
+        <v>10.71969724199924</v>
       </c>
       <c r="F273" t="n">
         <v>12</v>
@@ -17382,13 +17382,13 @@
         <v>13741.519596</v>
       </c>
       <c r="Q273" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R273" t="n">
         <v>1322.16</v>
       </c>
       <c r="S273" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T273" t="n">
         <v>3000</v>
@@ -17408,7 +17408,7 @@
         <v>1.856513018878587</v>
       </c>
       <c r="E274" t="n">
-        <v>11.48744131047166</v>
+        <v>11.4663939900049</v>
       </c>
       <c r="F274" t="n">
         <v>12</v>
@@ -17444,13 +17444,13 @@
         <v>41926.40559599999</v>
       </c>
       <c r="Q274" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R274" t="n">
         <v>1322.16</v>
       </c>
       <c r="S274" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T274" t="n">
         <v>3000</v>
@@ -17470,7 +17470,7 @@
         <v>5.569539056635763</v>
       </c>
       <c r="E275" t="n">
-        <v>11.48744131047166</v>
+        <v>11.4663939900049</v>
       </c>
       <c r="F275" t="n">
         <v>12</v>
@@ -17506,13 +17506,13 @@
         <v>41926.40559599999</v>
       </c>
       <c r="Q275" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R275" t="n">
         <v>1322.16</v>
       </c>
       <c r="S275" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T275" t="n">
         <v>3000</v>
@@ -17532,7 +17532,7 @@
         <v>5.479092502166411</v>
       </c>
       <c r="E276" t="n">
-        <v>10.740744562466</v>
+        <v>10.71969724199924</v>
       </c>
       <c r="F276" t="n">
         <v>12</v>
@@ -17568,13 +17568,13 @@
         <v>13741.519596</v>
       </c>
       <c r="Q276" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R276" t="n">
         <v>1322.16</v>
       </c>
       <c r="S276" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T276" t="n">
         <v>3000</v>
@@ -17594,7 +17594,7 @@
         <v>3.713026037757175</v>
       </c>
       <c r="E277" t="n">
-        <v>11.48744131047166</v>
+        <v>11.4663939900049</v>
       </c>
       <c r="F277" t="n">
         <v>12</v>
@@ -17630,13 +17630,13 @@
         <v>41926.40559599999</v>
       </c>
       <c r="Q277" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R277" t="n">
         <v>1322.16</v>
       </c>
       <c r="S277" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T277" t="n">
         <v>3000</v>
